--- a/annotation/异物类型核验表单.xlsx
+++ b/annotation/异物类型核验表单.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核验表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'核验表'!$A$1:$P$412</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'核验表'!$A$1:$Q$412</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C16"/>
+  <dimension ref="B2:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -604,25 +604,37 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>盲法</t>
+          <t>关于尺寸</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>表单刻意不含治疗方式、结局与初步诊断，避免因知道结局而改变判读。</t>
+          <t>只有 1.8%(22/1238) 的现病史写了具体尺寸，故本表不设测量字段——尺寸以 X 线实测为准，见 annotation/X线重标注表单.xlsx 的长径/短径列。「原文所述大小」仅为兜住这 1.8%，未写就留空，不要据描述估算。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>盲法</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>表单刻意不含治疗方式、结局与初步诊断，避免因知道结局而改变判读。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>完成之后</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>运行 python3 scripts/ingest_fbtype.py 表单.xlsx [第二位核验者.xlsx]</t>
         </is>
@@ -639,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P412"/>
+  <dimension ref="A1:Q412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -657,7 +669,8 @@
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -737,6 +750,11 @@
         </is>
       </c>
       <c r="P1" s="6" t="inlineStr">
+        <is>
+          <t>原文所述大小</t>
+        </is>
+      </c>
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -785,6 +803,7 @@
       <c r="N2" s="9" t="n"/>
       <c r="O2" s="9" t="n"/>
       <c r="P2" s="9" t="n"/>
+      <c r="Q2" s="9" t="n"/>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="9" t="n">
@@ -833,6 +852,7 @@
       <c r="N3" s="9" t="n"/>
       <c r="O3" s="9" t="n"/>
       <c r="P3" s="9" t="n"/>
+      <c r="Q3" s="9" t="n"/>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="7" t="n">
@@ -877,6 +897,7 @@
       <c r="N4" s="9" t="n"/>
       <c r="O4" s="9" t="n"/>
       <c r="P4" s="9" t="n"/>
+      <c r="Q4" s="9" t="n"/>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="9" t="n">
@@ -921,6 +942,7 @@
       <c r="N5" s="9" t="n"/>
       <c r="O5" s="9" t="n"/>
       <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="9" t="n"/>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="7" t="n">
@@ -961,6 +983,7 @@
       <c r="N6" s="9" t="n"/>
       <c r="O6" s="9" t="n"/>
       <c r="P6" s="9" t="n"/>
+      <c r="Q6" s="9" t="n"/>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="9" t="n">
@@ -1005,6 +1028,7 @@
       <c r="N7" s="9" t="n"/>
       <c r="O7" s="9" t="n"/>
       <c r="P7" s="9" t="n"/>
+      <c r="Q7" s="9" t="n"/>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="7" t="n">
@@ -1049,6 +1073,7 @@
       <c r="N8" s="9" t="n"/>
       <c r="O8" s="9" t="n"/>
       <c r="P8" s="9" t="n"/>
+      <c r="Q8" s="9" t="n"/>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="9" t="n">
@@ -1093,6 +1118,7 @@
       <c r="N9" s="9" t="n"/>
       <c r="O9" s="9" t="n"/>
       <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="9" t="n"/>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="7" t="n">
@@ -1141,6 +1167,7 @@
       <c r="N10" s="9" t="n"/>
       <c r="O10" s="9" t="n"/>
       <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="9" t="n"/>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="9" t="n">
@@ -1185,6 +1212,7 @@
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n"/>
       <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="9" t="n"/>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="7" t="n">
@@ -1229,6 +1257,7 @@
       <c r="N12" s="9" t="n"/>
       <c r="O12" s="9" t="n"/>
       <c r="P12" s="9" t="n"/>
+      <c r="Q12" s="9" t="n"/>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="9" t="n">
@@ -1273,6 +1302,7 @@
       <c r="N13" s="9" t="n"/>
       <c r="O13" s="9" t="n"/>
       <c r="P13" s="9" t="n"/>
+      <c r="Q13" s="9" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="7" t="n">
@@ -1317,6 +1347,7 @@
       <c r="N14" s="9" t="n"/>
       <c r="O14" s="9" t="n"/>
       <c r="P14" s="9" t="n"/>
+      <c r="Q14" s="9" t="n"/>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="9" t="n">
@@ -1361,6 +1392,7 @@
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
       <c r="P15" s="9" t="n"/>
+      <c r="Q15" s="9" t="n"/>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="7" t="n">
@@ -1409,6 +1441,7 @@
       <c r="N16" s="9" t="n"/>
       <c r="O16" s="9" t="n"/>
       <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="9" t="n"/>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="9" t="n">
@@ -1453,6 +1486,7 @@
       <c r="N17" s="9" t="n"/>
       <c r="O17" s="9" t="n"/>
       <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="9" t="n"/>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="7" t="n">
@@ -1497,6 +1531,7 @@
       <c r="N18" s="9" t="n"/>
       <c r="O18" s="9" t="n"/>
       <c r="P18" s="9" t="n"/>
+      <c r="Q18" s="9" t="n"/>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="9" t="n">
@@ -1541,6 +1576,7 @@
       <c r="N19" s="9" t="n"/>
       <c r="O19" s="9" t="n"/>
       <c r="P19" s="9" t="n"/>
+      <c r="Q19" s="9" t="n"/>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="7" t="n">
@@ -1585,6 +1621,7 @@
       <c r="N20" s="9" t="n"/>
       <c r="O20" s="9" t="n"/>
       <c r="P20" s="9" t="n"/>
+      <c r="Q20" s="9" t="n"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="9" t="n">
@@ -1633,6 +1670,7 @@
       <c r="N21" s="9" t="n"/>
       <c r="O21" s="9" t="n"/>
       <c r="P21" s="9" t="n"/>
+      <c r="Q21" s="9" t="n"/>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="7" t="n">
@@ -1677,6 +1715,7 @@
       <c r="N22" s="9" t="n"/>
       <c r="O22" s="9" t="n"/>
       <c r="P22" s="9" t="n"/>
+      <c r="Q22" s="9" t="n"/>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="9" t="n">
@@ -1725,6 +1764,7 @@
       <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
+      <c r="Q23" s="9" t="n"/>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="7" t="n">
@@ -1769,6 +1809,7 @@
       <c r="N24" s="9" t="n"/>
       <c r="O24" s="9" t="n"/>
       <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="9" t="n"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="9" t="n">
@@ -1817,6 +1858,7 @@
       <c r="N25" s="9" t="n"/>
       <c r="O25" s="9" t="n"/>
       <c r="P25" s="9" t="n"/>
+      <c r="Q25" s="9" t="n"/>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="7" t="n">
@@ -1861,6 +1903,7 @@
       <c r="N26" s="9" t="n"/>
       <c r="O26" s="9" t="n"/>
       <c r="P26" s="9" t="n"/>
+      <c r="Q26" s="9" t="n"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="9" t="n">
@@ -1905,6 +1948,7 @@
       <c r="N27" s="9" t="n"/>
       <c r="O27" s="9" t="n"/>
       <c r="P27" s="9" t="n"/>
+      <c r="Q27" s="9" t="n"/>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="7" t="n">
@@ -1949,6 +1993,7 @@
       <c r="N28" s="9" t="n"/>
       <c r="O28" s="9" t="n"/>
       <c r="P28" s="9" t="n"/>
+      <c r="Q28" s="9" t="n"/>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="9" t="n">
@@ -1993,6 +2038,7 @@
       <c r="N29" s="9" t="n"/>
       <c r="O29" s="9" t="n"/>
       <c r="P29" s="9" t="n"/>
+      <c r="Q29" s="9" t="n"/>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="7" t="n">
@@ -2033,6 +2079,7 @@
       <c r="N30" s="9" t="n"/>
       <c r="O30" s="9" t="n"/>
       <c r="P30" s="9" t="n"/>
+      <c r="Q30" s="9" t="n"/>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="9" t="n">
@@ -2077,6 +2124,7 @@
       <c r="N31" s="9" t="n"/>
       <c r="O31" s="9" t="n"/>
       <c r="P31" s="9" t="n"/>
+      <c r="Q31" s="9" t="n"/>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="7" t="n">
@@ -2121,6 +2169,7 @@
       <c r="N32" s="9" t="n"/>
       <c r="O32" s="9" t="n"/>
       <c r="P32" s="9" t="n"/>
+      <c r="Q32" s="9" t="n"/>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="9" t="n">
@@ -2165,6 +2214,7 @@
       <c r="N33" s="9" t="n"/>
       <c r="O33" s="9" t="n"/>
       <c r="P33" s="9" t="n"/>
+      <c r="Q33" s="9" t="n"/>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="7" t="n">
@@ -2209,6 +2259,7 @@
       <c r="N34" s="9" t="n"/>
       <c r="O34" s="9" t="n"/>
       <c r="P34" s="9" t="n"/>
+      <c r="Q34" s="9" t="n"/>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="9" t="n">
@@ -2253,6 +2304,7 @@
       <c r="N35" s="9" t="n"/>
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
+      <c r="Q35" s="9" t="n"/>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="7" t="n">
@@ -2297,6 +2349,7 @@
       <c r="N36" s="9" t="n"/>
       <c r="O36" s="9" t="n"/>
       <c r="P36" s="9" t="n"/>
+      <c r="Q36" s="9" t="n"/>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="9" t="n">
@@ -2341,6 +2394,7 @@
       <c r="N37" s="9" t="n"/>
       <c r="O37" s="9" t="n"/>
       <c r="P37" s="9" t="n"/>
+      <c r="Q37" s="9" t="n"/>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="7" t="n">
@@ -2385,6 +2439,7 @@
       <c r="N38" s="9" t="n"/>
       <c r="O38" s="9" t="n"/>
       <c r="P38" s="9" t="n"/>
+      <c r="Q38" s="9" t="n"/>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="9" t="n">
@@ -2433,6 +2488,7 @@
       <c r="N39" s="9" t="n"/>
       <c r="O39" s="9" t="n"/>
       <c r="P39" s="9" t="n"/>
+      <c r="Q39" s="9" t="n"/>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="7" t="n">
@@ -2481,6 +2537,7 @@
       <c r="N40" s="9" t="n"/>
       <c r="O40" s="9" t="n"/>
       <c r="P40" s="9" t="n"/>
+      <c r="Q40" s="9" t="n"/>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="9" t="n">
@@ -2525,6 +2582,7 @@
       <c r="N41" s="9" t="n"/>
       <c r="O41" s="9" t="n"/>
       <c r="P41" s="9" t="n"/>
+      <c r="Q41" s="9" t="n"/>
     </row>
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="7" t="n">
@@ -2573,6 +2631,7 @@
       <c r="N42" s="9" t="n"/>
       <c r="O42" s="9" t="n"/>
       <c r="P42" s="9" t="n"/>
+      <c r="Q42" s="9" t="n"/>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="9" t="n">
@@ -2617,6 +2676,7 @@
       <c r="N43" s="9" t="n"/>
       <c r="O43" s="9" t="n"/>
       <c r="P43" s="9" t="n"/>
+      <c r="Q43" s="9" t="n"/>
     </row>
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="7" t="n">
@@ -2661,6 +2721,7 @@
       <c r="N44" s="9" t="n"/>
       <c r="O44" s="9" t="n"/>
       <c r="P44" s="9" t="n"/>
+      <c r="Q44" s="9" t="n"/>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="9" t="n">
@@ -2705,6 +2766,7 @@
       <c r="N45" s="9" t="n"/>
       <c r="O45" s="9" t="n"/>
       <c r="P45" s="9" t="n"/>
+      <c r="Q45" s="9" t="n"/>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="7" t="n">
@@ -2753,6 +2815,7 @@
       <c r="N46" s="9" t="n"/>
       <c r="O46" s="9" t="n"/>
       <c r="P46" s="9" t="n"/>
+      <c r="Q46" s="9" t="n"/>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="9" t="n">
@@ -2801,6 +2864,7 @@
       <c r="N47" s="9" t="n"/>
       <c r="O47" s="9" t="n"/>
       <c r="P47" s="9" t="n"/>
+      <c r="Q47" s="9" t="n"/>
     </row>
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="7" t="n">
@@ -2849,6 +2913,7 @@
       <c r="N48" s="9" t="n"/>
       <c r="O48" s="9" t="n"/>
       <c r="P48" s="9" t="n"/>
+      <c r="Q48" s="9" t="n"/>
     </row>
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="9" t="n">
@@ -2893,6 +2958,7 @@
       <c r="N49" s="9" t="n"/>
       <c r="O49" s="9" t="n"/>
       <c r="P49" s="9" t="n"/>
+      <c r="Q49" s="9" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="7" t="n">
@@ -2937,6 +3003,7 @@
       <c r="N50" s="9" t="n"/>
       <c r="O50" s="9" t="n"/>
       <c r="P50" s="9" t="n"/>
+      <c r="Q50" s="9" t="n"/>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="9" t="n">
@@ -2981,6 +3048,7 @@
       <c r="N51" s="9" t="n"/>
       <c r="O51" s="9" t="n"/>
       <c r="P51" s="9" t="n"/>
+      <c r="Q51" s="9" t="n"/>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="7" t="n">
@@ -3025,6 +3093,7 @@
       <c r="N52" s="9" t="n"/>
       <c r="O52" s="9" t="n"/>
       <c r="P52" s="9" t="n"/>
+      <c r="Q52" s="9" t="n"/>
     </row>
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="9" t="n">
@@ -3069,6 +3138,7 @@
       <c r="N53" s="9" t="n"/>
       <c r="O53" s="9" t="n"/>
       <c r="P53" s="9" t="n"/>
+      <c r="Q53" s="9" t="n"/>
     </row>
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="7" t="n">
@@ -3113,6 +3183,7 @@
       <c r="N54" s="9" t="n"/>
       <c r="O54" s="9" t="n"/>
       <c r="P54" s="9" t="n"/>
+      <c r="Q54" s="9" t="n"/>
     </row>
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="9" t="n">
@@ -3157,6 +3228,7 @@
       <c r="N55" s="9" t="n"/>
       <c r="O55" s="9" t="n"/>
       <c r="P55" s="9" t="n"/>
+      <c r="Q55" s="9" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="7" t="n">
@@ -3205,6 +3277,7 @@
       <c r="N56" s="9" t="n"/>
       <c r="O56" s="9" t="n"/>
       <c r="P56" s="9" t="n"/>
+      <c r="Q56" s="9" t="n"/>
     </row>
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="9" t="n">
@@ -3249,6 +3322,7 @@
       <c r="N57" s="9" t="n"/>
       <c r="O57" s="9" t="n"/>
       <c r="P57" s="9" t="n"/>
+      <c r="Q57" s="9" t="n"/>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="7" t="n">
@@ -3297,6 +3371,7 @@
       <c r="N58" s="9" t="n"/>
       <c r="O58" s="9" t="n"/>
       <c r="P58" s="9" t="n"/>
+      <c r="Q58" s="9" t="n"/>
     </row>
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="9" t="n">
@@ -3341,6 +3416,7 @@
       <c r="N59" s="9" t="n"/>
       <c r="O59" s="9" t="n"/>
       <c r="P59" s="9" t="n"/>
+      <c r="Q59" s="9" t="n"/>
     </row>
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="7" t="n">
@@ -3385,6 +3461,7 @@
       <c r="N60" s="9" t="n"/>
       <c r="O60" s="9" t="n"/>
       <c r="P60" s="9" t="n"/>
+      <c r="Q60" s="9" t="n"/>
     </row>
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="9" t="n">
@@ -3429,6 +3506,7 @@
       <c r="N61" s="9" t="n"/>
       <c r="O61" s="9" t="n"/>
       <c r="P61" s="9" t="n"/>
+      <c r="Q61" s="9" t="n"/>
     </row>
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="7" t="n">
@@ -3473,6 +3551,7 @@
       <c r="N62" s="9" t="n"/>
       <c r="O62" s="9" t="n"/>
       <c r="P62" s="9" t="n"/>
+      <c r="Q62" s="9" t="n"/>
     </row>
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="9" t="n">
@@ -3517,6 +3596,7 @@
       <c r="N63" s="9" t="n"/>
       <c r="O63" s="9" t="n"/>
       <c r="P63" s="9" t="n"/>
+      <c r="Q63" s="9" t="n"/>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="7" t="n">
@@ -3561,6 +3641,7 @@
       <c r="N64" s="9" t="n"/>
       <c r="O64" s="9" t="n"/>
       <c r="P64" s="9" t="n"/>
+      <c r="Q64" s="9" t="n"/>
     </row>
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="9" t="n">
@@ -3605,6 +3686,7 @@
       <c r="N65" s="9" t="n"/>
       <c r="O65" s="9" t="n"/>
       <c r="P65" s="9" t="n"/>
+      <c r="Q65" s="9" t="n"/>
     </row>
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="7" t="n">
@@ -3649,6 +3731,7 @@
       <c r="N66" s="9" t="n"/>
       <c r="O66" s="9" t="n"/>
       <c r="P66" s="9" t="n"/>
+      <c r="Q66" s="9" t="n"/>
     </row>
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="9" t="n">
@@ -3693,6 +3776,7 @@
       <c r="N67" s="9" t="n"/>
       <c r="O67" s="9" t="n"/>
       <c r="P67" s="9" t="n"/>
+      <c r="Q67" s="9" t="n"/>
     </row>
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="7" t="n">
@@ -3737,6 +3821,7 @@
       <c r="N68" s="9" t="n"/>
       <c r="O68" s="9" t="n"/>
       <c r="P68" s="9" t="n"/>
+      <c r="Q68" s="9" t="n"/>
     </row>
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="9" t="n">
@@ -3781,6 +3866,7 @@
       <c r="N69" s="9" t="n"/>
       <c r="O69" s="9" t="n"/>
       <c r="P69" s="9" t="n"/>
+      <c r="Q69" s="9" t="n"/>
     </row>
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="7" t="n">
@@ -3825,6 +3911,7 @@
       <c r="N70" s="9" t="n"/>
       <c r="O70" s="9" t="n"/>
       <c r="P70" s="9" t="n"/>
+      <c r="Q70" s="9" t="n"/>
     </row>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="9" t="n">
@@ -3869,6 +3956,7 @@
       <c r="N71" s="9" t="n"/>
       <c r="O71" s="9" t="n"/>
       <c r="P71" s="9" t="n"/>
+      <c r="Q71" s="9" t="n"/>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="7" t="n">
@@ -3913,6 +4001,7 @@
       <c r="N72" s="9" t="n"/>
       <c r="O72" s="9" t="n"/>
       <c r="P72" s="9" t="n"/>
+      <c r="Q72" s="9" t="n"/>
     </row>
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="9" t="n">
@@ -3957,6 +4046,7 @@
       <c r="N73" s="9" t="n"/>
       <c r="O73" s="9" t="n"/>
       <c r="P73" s="9" t="n"/>
+      <c r="Q73" s="9" t="n"/>
     </row>
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="7" t="n">
@@ -4001,6 +4091,7 @@
       <c r="N74" s="9" t="n"/>
       <c r="O74" s="9" t="n"/>
       <c r="P74" s="9" t="n"/>
+      <c r="Q74" s="9" t="n"/>
     </row>
     <row r="75" ht="42" customHeight="1">
       <c r="A75" s="9" t="n">
@@ -4045,6 +4136,7 @@
       <c r="N75" s="9" t="n"/>
       <c r="O75" s="9" t="n"/>
       <c r="P75" s="9" t="n"/>
+      <c r="Q75" s="9" t="n"/>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="7" t="n">
@@ -4089,6 +4181,7 @@
       <c r="N76" s="9" t="n"/>
       <c r="O76" s="9" t="n"/>
       <c r="P76" s="9" t="n"/>
+      <c r="Q76" s="9" t="n"/>
     </row>
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="9" t="n">
@@ -4133,6 +4226,7 @@
       <c r="N77" s="9" t="n"/>
       <c r="O77" s="9" t="n"/>
       <c r="P77" s="9" t="n"/>
+      <c r="Q77" s="9" t="n"/>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="7" t="n">
@@ -4177,6 +4271,7 @@
       <c r="N78" s="9" t="n"/>
       <c r="O78" s="9" t="n"/>
       <c r="P78" s="9" t="n"/>
+      <c r="Q78" s="9" t="n"/>
     </row>
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="9" t="n">
@@ -4217,6 +4312,7 @@
       <c r="N79" s="9" t="n"/>
       <c r="O79" s="9" t="n"/>
       <c r="P79" s="9" t="n"/>
+      <c r="Q79" s="9" t="n"/>
     </row>
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="7" t="n">
@@ -4257,6 +4353,7 @@
       <c r="N80" s="9" t="n"/>
       <c r="O80" s="9" t="n"/>
       <c r="P80" s="9" t="n"/>
+      <c r="Q80" s="9" t="n"/>
     </row>
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="9" t="n">
@@ -4301,6 +4398,7 @@
       <c r="N81" s="9" t="n"/>
       <c r="O81" s="9" t="n"/>
       <c r="P81" s="9" t="n"/>
+      <c r="Q81" s="9" t="n"/>
     </row>
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="7" t="n">
@@ -4345,6 +4443,7 @@
       <c r="N82" s="9" t="n"/>
       <c r="O82" s="9" t="n"/>
       <c r="P82" s="9" t="n"/>
+      <c r="Q82" s="9" t="n"/>
     </row>
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="9" t="n">
@@ -4389,6 +4488,7 @@
       <c r="N83" s="9" t="n"/>
       <c r="O83" s="9" t="n"/>
       <c r="P83" s="9" t="n"/>
+      <c r="Q83" s="9" t="n"/>
     </row>
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="7" t="n">
@@ -4433,6 +4533,7 @@
       <c r="N84" s="9" t="n"/>
       <c r="O84" s="9" t="n"/>
       <c r="P84" s="9" t="n"/>
+      <c r="Q84" s="9" t="n"/>
     </row>
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="9" t="n">
@@ -4477,6 +4578,7 @@
       <c r="N85" s="9" t="n"/>
       <c r="O85" s="9" t="n"/>
       <c r="P85" s="9" t="n"/>
+      <c r="Q85" s="9" t="n"/>
     </row>
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="7" t="n">
@@ -4521,6 +4623,7 @@
       <c r="N86" s="9" t="n"/>
       <c r="O86" s="9" t="n"/>
       <c r="P86" s="9" t="n"/>
+      <c r="Q86" s="9" t="n"/>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="9" t="n">
@@ -4569,6 +4672,7 @@
       <c r="N87" s="9" t="n"/>
       <c r="O87" s="9" t="n"/>
       <c r="P87" s="9" t="n"/>
+      <c r="Q87" s="9" t="n"/>
     </row>
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="7" t="n">
@@ -4613,6 +4717,7 @@
       <c r="N88" s="9" t="n"/>
       <c r="O88" s="9" t="n"/>
       <c r="P88" s="9" t="n"/>
+      <c r="Q88" s="9" t="n"/>
     </row>
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="9" t="n">
@@ -4657,6 +4762,7 @@
       <c r="N89" s="9" t="n"/>
       <c r="O89" s="9" t="n"/>
       <c r="P89" s="9" t="n"/>
+      <c r="Q89" s="9" t="n"/>
     </row>
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="7" t="n">
@@ -4701,6 +4807,7 @@
       <c r="N90" s="9" t="n"/>
       <c r="O90" s="9" t="n"/>
       <c r="P90" s="9" t="n"/>
+      <c r="Q90" s="9" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="9" t="n">
@@ -4745,6 +4852,7 @@
       <c r="N91" s="9" t="n"/>
       <c r="O91" s="9" t="n"/>
       <c r="P91" s="9" t="n"/>
+      <c r="Q91" s="9" t="n"/>
     </row>
     <row r="92" ht="42" customHeight="1">
       <c r="A92" s="7" t="n">
@@ -4789,6 +4897,7 @@
       <c r="N92" s="9" t="n"/>
       <c r="O92" s="9" t="n"/>
       <c r="P92" s="9" t="n"/>
+      <c r="Q92" s="9" t="n"/>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="9" t="n">
@@ -4833,6 +4942,7 @@
       <c r="N93" s="9" t="n"/>
       <c r="O93" s="9" t="n"/>
       <c r="P93" s="9" t="n"/>
+      <c r="Q93" s="9" t="n"/>
     </row>
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="7" t="n">
@@ -4877,6 +4987,7 @@
       <c r="N94" s="9" t="n"/>
       <c r="O94" s="9" t="n"/>
       <c r="P94" s="9" t="n"/>
+      <c r="Q94" s="9" t="n"/>
     </row>
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="9" t="n">
@@ -4925,6 +5036,7 @@
       <c r="N95" s="9" t="n"/>
       <c r="O95" s="9" t="n"/>
       <c r="P95" s="9" t="n"/>
+      <c r="Q95" s="9" t="n"/>
     </row>
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="7" t="n">
@@ -4969,6 +5081,7 @@
       <c r="N96" s="9" t="n"/>
       <c r="O96" s="9" t="n"/>
       <c r="P96" s="9" t="n"/>
+      <c r="Q96" s="9" t="n"/>
     </row>
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="9" t="n">
@@ -5013,6 +5126,7 @@
       <c r="N97" s="9" t="n"/>
       <c r="O97" s="9" t="n"/>
       <c r="P97" s="9" t="n"/>
+      <c r="Q97" s="9" t="n"/>
     </row>
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="7" t="n">
@@ -5061,6 +5175,7 @@
       <c r="N98" s="9" t="n"/>
       <c r="O98" s="9" t="n"/>
       <c r="P98" s="9" t="n"/>
+      <c r="Q98" s="9" t="n"/>
     </row>
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="9" t="n">
@@ -5105,6 +5220,7 @@
       <c r="N99" s="9" t="n"/>
       <c r="O99" s="9" t="n"/>
       <c r="P99" s="9" t="n"/>
+      <c r="Q99" s="9" t="n"/>
     </row>
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="7" t="n">
@@ -5149,6 +5265,7 @@
       <c r="N100" s="9" t="n"/>
       <c r="O100" s="9" t="n"/>
       <c r="P100" s="9" t="n"/>
+      <c r="Q100" s="9" t="n"/>
     </row>
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="9" t="n">
@@ -5193,6 +5310,7 @@
       <c r="N101" s="9" t="n"/>
       <c r="O101" s="9" t="n"/>
       <c r="P101" s="9" t="n"/>
+      <c r="Q101" s="9" t="n"/>
     </row>
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="7" t="n">
@@ -5237,6 +5355,7 @@
       <c r="N102" s="9" t="n"/>
       <c r="O102" s="9" t="n"/>
       <c r="P102" s="9" t="n"/>
+      <c r="Q102" s="9" t="n"/>
     </row>
     <row r="103" ht="42" customHeight="1">
       <c r="A103" s="9" t="n">
@@ -5281,6 +5400,7 @@
       <c r="N103" s="9" t="n"/>
       <c r="O103" s="9" t="n"/>
       <c r="P103" s="9" t="n"/>
+      <c r="Q103" s="9" t="n"/>
     </row>
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="7" t="n">
@@ -5325,6 +5445,7 @@
       <c r="N104" s="9" t="n"/>
       <c r="O104" s="9" t="n"/>
       <c r="P104" s="9" t="n"/>
+      <c r="Q104" s="9" t="n"/>
     </row>
     <row r="105" ht="42" customHeight="1">
       <c r="A105" s="9" t="n">
@@ -5373,6 +5494,7 @@
       <c r="N105" s="9" t="n"/>
       <c r="O105" s="9" t="n"/>
       <c r="P105" s="9" t="n"/>
+      <c r="Q105" s="9" t="n"/>
     </row>
     <row r="106" ht="42" customHeight="1">
       <c r="A106" s="7" t="n">
@@ -5417,6 +5539,7 @@
       <c r="N106" s="9" t="n"/>
       <c r="O106" s="9" t="n"/>
       <c r="P106" s="9" t="n"/>
+      <c r="Q106" s="9" t="n"/>
     </row>
     <row r="107" ht="42" customHeight="1">
       <c r="A107" s="9" t="n">
@@ -5461,6 +5584,7 @@
       <c r="N107" s="9" t="n"/>
       <c r="O107" s="9" t="n"/>
       <c r="P107" s="9" t="n"/>
+      <c r="Q107" s="9" t="n"/>
     </row>
     <row r="108" ht="42" customHeight="1">
       <c r="A108" s="7" t="n">
@@ -5505,6 +5629,7 @@
       <c r="N108" s="9" t="n"/>
       <c r="O108" s="9" t="n"/>
       <c r="P108" s="9" t="n"/>
+      <c r="Q108" s="9" t="n"/>
     </row>
     <row r="109" ht="42" customHeight="1">
       <c r="A109" s="9" t="n">
@@ -5549,6 +5674,7 @@
       <c r="N109" s="9" t="n"/>
       <c r="O109" s="9" t="n"/>
       <c r="P109" s="9" t="n"/>
+      <c r="Q109" s="9" t="n"/>
     </row>
     <row r="110" ht="42" customHeight="1">
       <c r="A110" s="7" t="n">
@@ -5593,6 +5719,7 @@
       <c r="N110" s="9" t="n"/>
       <c r="O110" s="9" t="n"/>
       <c r="P110" s="9" t="n"/>
+      <c r="Q110" s="9" t="n"/>
     </row>
     <row r="111" ht="42" customHeight="1">
       <c r="A111" s="9" t="n">
@@ -5633,6 +5760,7 @@
       <c r="N111" s="9" t="n"/>
       <c r="O111" s="9" t="n"/>
       <c r="P111" s="9" t="n"/>
+      <c r="Q111" s="9" t="n"/>
     </row>
     <row r="112" ht="42" customHeight="1">
       <c r="A112" s="7" t="n">
@@ -5677,6 +5805,7 @@
       <c r="N112" s="9" t="n"/>
       <c r="O112" s="9" t="n"/>
       <c r="P112" s="9" t="n"/>
+      <c r="Q112" s="9" t="n"/>
     </row>
     <row r="113" ht="42" customHeight="1">
       <c r="A113" s="9" t="n">
@@ -5725,6 +5854,7 @@
       <c r="N113" s="9" t="n"/>
       <c r="O113" s="9" t="n"/>
       <c r="P113" s="9" t="n"/>
+      <c r="Q113" s="9" t="n"/>
     </row>
     <row r="114" ht="42" customHeight="1">
       <c r="A114" s="7" t="n">
@@ -5769,6 +5899,7 @@
       <c r="N114" s="9" t="n"/>
       <c r="O114" s="9" t="n"/>
       <c r="P114" s="9" t="n"/>
+      <c r="Q114" s="9" t="n"/>
     </row>
     <row r="115" ht="42" customHeight="1">
       <c r="A115" s="9" t="n">
@@ -5817,6 +5948,7 @@
       <c r="N115" s="9" t="n"/>
       <c r="O115" s="9" t="n"/>
       <c r="P115" s="9" t="n"/>
+      <c r="Q115" s="9" t="n"/>
     </row>
     <row r="116" ht="42" customHeight="1">
       <c r="A116" s="7" t="n">
@@ -5865,6 +5997,7 @@
       <c r="N116" s="9" t="n"/>
       <c r="O116" s="9" t="n"/>
       <c r="P116" s="9" t="n"/>
+      <c r="Q116" s="9" t="n"/>
     </row>
     <row r="117" ht="42" customHeight="1">
       <c r="A117" s="9" t="n">
@@ -5913,6 +6046,7 @@
       <c r="N117" s="9" t="n"/>
       <c r="O117" s="9" t="n"/>
       <c r="P117" s="9" t="n"/>
+      <c r="Q117" s="9" t="n"/>
     </row>
     <row r="118" ht="42" customHeight="1">
       <c r="A118" s="7" t="n">
@@ -5961,6 +6095,7 @@
       <c r="N118" s="9" t="n"/>
       <c r="O118" s="9" t="n"/>
       <c r="P118" s="9" t="n"/>
+      <c r="Q118" s="9" t="n"/>
     </row>
     <row r="119" ht="42" customHeight="1">
       <c r="A119" s="9" t="n">
@@ -6005,6 +6140,7 @@
       <c r="N119" s="9" t="n"/>
       <c r="O119" s="9" t="n"/>
       <c r="P119" s="9" t="n"/>
+      <c r="Q119" s="9" t="n"/>
     </row>
     <row r="120" ht="42" customHeight="1">
       <c r="A120" s="7" t="n">
@@ -6049,6 +6185,7 @@
       <c r="N120" s="9" t="n"/>
       <c r="O120" s="9" t="n"/>
       <c r="P120" s="9" t="n"/>
+      <c r="Q120" s="9" t="n"/>
     </row>
     <row r="121" ht="42" customHeight="1">
       <c r="A121" s="9" t="n">
@@ -6093,6 +6230,7 @@
       <c r="N121" s="9" t="n"/>
       <c r="O121" s="9" t="n"/>
       <c r="P121" s="9" t="n"/>
+      <c r="Q121" s="9" t="n"/>
     </row>
     <row r="122" ht="42" customHeight="1">
       <c r="A122" s="7" t="n">
@@ -6137,6 +6275,7 @@
       <c r="N122" s="9" t="n"/>
       <c r="O122" s="9" t="n"/>
       <c r="P122" s="9" t="n"/>
+      <c r="Q122" s="9" t="n"/>
     </row>
     <row r="123" ht="42" customHeight="1">
       <c r="A123" s="9" t="n">
@@ -6181,6 +6320,7 @@
       <c r="N123" s="9" t="n"/>
       <c r="O123" s="9" t="n"/>
       <c r="P123" s="9" t="n"/>
+      <c r="Q123" s="9" t="n"/>
     </row>
     <row r="124" ht="42" customHeight="1">
       <c r="A124" s="7" t="n">
@@ -6225,6 +6365,7 @@
       <c r="N124" s="9" t="n"/>
       <c r="O124" s="9" t="n"/>
       <c r="P124" s="9" t="n"/>
+      <c r="Q124" s="9" t="n"/>
     </row>
     <row r="125" ht="42" customHeight="1">
       <c r="A125" s="9" t="n">
@@ -6269,6 +6410,7 @@
       <c r="N125" s="9" t="n"/>
       <c r="O125" s="9" t="n"/>
       <c r="P125" s="9" t="n"/>
+      <c r="Q125" s="9" t="n"/>
     </row>
     <row r="126" ht="42" customHeight="1">
       <c r="A126" s="7" t="n">
@@ -6313,6 +6455,7 @@
       <c r="N126" s="9" t="n"/>
       <c r="O126" s="9" t="n"/>
       <c r="P126" s="9" t="n"/>
+      <c r="Q126" s="9" t="n"/>
     </row>
     <row r="127" ht="42" customHeight="1">
       <c r="A127" s="9" t="n">
@@ -6357,6 +6500,7 @@
       <c r="N127" s="9" t="n"/>
       <c r="O127" s="9" t="n"/>
       <c r="P127" s="9" t="n"/>
+      <c r="Q127" s="9" t="n"/>
     </row>
     <row r="128" ht="42" customHeight="1">
       <c r="A128" s="7" t="n">
@@ -6401,6 +6545,7 @@
       <c r="N128" s="9" t="n"/>
       <c r="O128" s="9" t="n"/>
       <c r="P128" s="9" t="n"/>
+      <c r="Q128" s="9" t="n"/>
     </row>
     <row r="129" ht="42" customHeight="1">
       <c r="A129" s="9" t="n">
@@ -6445,6 +6590,7 @@
       <c r="N129" s="9" t="n"/>
       <c r="O129" s="9" t="n"/>
       <c r="P129" s="9" t="n"/>
+      <c r="Q129" s="9" t="n"/>
     </row>
     <row r="130" ht="42" customHeight="1">
       <c r="A130" s="7" t="n">
@@ -6489,6 +6635,7 @@
       <c r="N130" s="9" t="n"/>
       <c r="O130" s="9" t="n"/>
       <c r="P130" s="9" t="n"/>
+      <c r="Q130" s="9" t="n"/>
     </row>
     <row r="131" ht="42" customHeight="1">
       <c r="A131" s="9" t="n">
@@ -6537,6 +6684,7 @@
       <c r="N131" s="9" t="n"/>
       <c r="O131" s="9" t="n"/>
       <c r="P131" s="9" t="n"/>
+      <c r="Q131" s="9" t="n"/>
     </row>
     <row r="132" ht="42" customHeight="1">
       <c r="A132" s="7" t="n">
@@ -6581,6 +6729,7 @@
       <c r="N132" s="9" t="n"/>
       <c r="O132" s="9" t="n"/>
       <c r="P132" s="9" t="n"/>
+      <c r="Q132" s="9" t="n"/>
     </row>
     <row r="133" ht="42" customHeight="1">
       <c r="A133" s="9" t="n">
@@ -6629,6 +6778,7 @@
       <c r="N133" s="9" t="n"/>
       <c r="O133" s="9" t="n"/>
       <c r="P133" s="9" t="n"/>
+      <c r="Q133" s="9" t="n"/>
     </row>
     <row r="134" ht="42" customHeight="1">
       <c r="A134" s="7" t="n">
@@ -6669,6 +6819,7 @@
       <c r="N134" s="9" t="n"/>
       <c r="O134" s="9" t="n"/>
       <c r="P134" s="9" t="n"/>
+      <c r="Q134" s="9" t="n"/>
     </row>
     <row r="135" ht="42" customHeight="1">
       <c r="A135" s="9" t="n">
@@ -6713,6 +6864,7 @@
       <c r="N135" s="9" t="n"/>
       <c r="O135" s="9" t="n"/>
       <c r="P135" s="9" t="n"/>
+      <c r="Q135" s="9" t="n"/>
     </row>
     <row r="136" ht="42" customHeight="1">
       <c r="A136" s="7" t="n">
@@ -6757,6 +6909,7 @@
       <c r="N136" s="9" t="n"/>
       <c r="O136" s="9" t="n"/>
       <c r="P136" s="9" t="n"/>
+      <c r="Q136" s="9" t="n"/>
     </row>
     <row r="137" ht="42" customHeight="1">
       <c r="A137" s="9" t="n">
@@ -6805,6 +6958,7 @@
       <c r="N137" s="9" t="n"/>
       <c r="O137" s="9" t="n"/>
       <c r="P137" s="9" t="n"/>
+      <c r="Q137" s="9" t="n"/>
     </row>
     <row r="138" ht="42" customHeight="1">
       <c r="A138" s="7" t="n">
@@ -6849,6 +7003,7 @@
       <c r="N138" s="9" t="n"/>
       <c r="O138" s="9" t="n"/>
       <c r="P138" s="9" t="n"/>
+      <c r="Q138" s="9" t="n"/>
     </row>
     <row r="139" ht="42" customHeight="1">
       <c r="A139" s="9" t="n">
@@ -6897,6 +7052,7 @@
       <c r="N139" s="9" t="n"/>
       <c r="O139" s="9" t="n"/>
       <c r="P139" s="9" t="n"/>
+      <c r="Q139" s="9" t="n"/>
     </row>
     <row r="140" ht="42" customHeight="1">
       <c r="A140" s="7" t="n">
@@ -6941,6 +7097,7 @@
       <c r="N140" s="9" t="n"/>
       <c r="O140" s="9" t="n"/>
       <c r="P140" s="9" t="n"/>
+      <c r="Q140" s="9" t="n"/>
     </row>
     <row r="141" ht="42" customHeight="1">
       <c r="A141" s="9" t="n">
@@ -6985,6 +7142,7 @@
       <c r="N141" s="9" t="n"/>
       <c r="O141" s="9" t="n"/>
       <c r="P141" s="9" t="n"/>
+      <c r="Q141" s="9" t="n"/>
     </row>
     <row r="142" ht="42" customHeight="1">
       <c r="A142" s="7" t="n">
@@ -7029,6 +7187,7 @@
       <c r="N142" s="9" t="n"/>
       <c r="O142" s="9" t="n"/>
       <c r="P142" s="9" t="n"/>
+      <c r="Q142" s="9" t="n"/>
     </row>
     <row r="143" ht="42" customHeight="1">
       <c r="A143" s="9" t="n">
@@ -7073,6 +7232,7 @@
       <c r="N143" s="9" t="n"/>
       <c r="O143" s="9" t="n"/>
       <c r="P143" s="9" t="n"/>
+      <c r="Q143" s="9" t="n"/>
     </row>
     <row r="144" ht="42" customHeight="1">
       <c r="A144" s="7" t="n">
@@ -7121,6 +7281,7 @@
       <c r="N144" s="9" t="n"/>
       <c r="O144" s="9" t="n"/>
       <c r="P144" s="9" t="n"/>
+      <c r="Q144" s="9" t="n"/>
     </row>
     <row r="145" ht="42" customHeight="1">
       <c r="A145" s="9" t="n">
@@ -7165,6 +7326,7 @@
       <c r="N145" s="9" t="n"/>
       <c r="O145" s="9" t="n"/>
       <c r="P145" s="9" t="n"/>
+      <c r="Q145" s="9" t="n"/>
     </row>
     <row r="146" ht="42" customHeight="1">
       <c r="A146" s="7" t="n">
@@ -7209,6 +7371,7 @@
       <c r="N146" s="9" t="n"/>
       <c r="O146" s="9" t="n"/>
       <c r="P146" s="9" t="n"/>
+      <c r="Q146" s="9" t="n"/>
     </row>
     <row r="147" ht="42" customHeight="1">
       <c r="A147" s="9" t="n">
@@ -7257,6 +7420,7 @@
       <c r="N147" s="9" t="n"/>
       <c r="O147" s="9" t="n"/>
       <c r="P147" s="9" t="n"/>
+      <c r="Q147" s="9" t="n"/>
     </row>
     <row r="148" ht="42" customHeight="1">
       <c r="A148" s="7" t="n">
@@ -7301,6 +7465,7 @@
       <c r="N148" s="9" t="n"/>
       <c r="O148" s="9" t="n"/>
       <c r="P148" s="9" t="n"/>
+      <c r="Q148" s="9" t="n"/>
     </row>
     <row r="149" ht="42" customHeight="1">
       <c r="A149" s="9" t="n">
@@ -7345,6 +7510,7 @@
       <c r="N149" s="9" t="n"/>
       <c r="O149" s="9" t="n"/>
       <c r="P149" s="9" t="n"/>
+      <c r="Q149" s="9" t="n"/>
     </row>
     <row r="150" ht="42" customHeight="1">
       <c r="A150" s="7" t="n">
@@ -7389,6 +7555,7 @@
       <c r="N150" s="9" t="n"/>
       <c r="O150" s="9" t="n"/>
       <c r="P150" s="9" t="n"/>
+      <c r="Q150" s="9" t="n"/>
     </row>
     <row r="151" ht="42" customHeight="1">
       <c r="A151" s="9" t="n">
@@ -7433,6 +7600,7 @@
       <c r="N151" s="9" t="n"/>
       <c r="O151" s="9" t="n"/>
       <c r="P151" s="9" t="n"/>
+      <c r="Q151" s="9" t="n"/>
     </row>
     <row r="152" ht="42" customHeight="1">
       <c r="A152" s="7" t="n">
@@ -7477,6 +7645,7 @@
       <c r="N152" s="9" t="n"/>
       <c r="O152" s="9" t="n"/>
       <c r="P152" s="9" t="n"/>
+      <c r="Q152" s="9" t="n"/>
     </row>
     <row r="153" ht="42" customHeight="1">
       <c r="A153" s="9" t="n">
@@ -7521,6 +7690,7 @@
       <c r="N153" s="9" t="n"/>
       <c r="O153" s="9" t="n"/>
       <c r="P153" s="9" t="n"/>
+      <c r="Q153" s="9" t="n"/>
     </row>
     <row r="154" ht="42" customHeight="1">
       <c r="A154" s="7" t="n">
@@ -7565,6 +7735,7 @@
       <c r="N154" s="9" t="n"/>
       <c r="O154" s="9" t="n"/>
       <c r="P154" s="9" t="n"/>
+      <c r="Q154" s="9" t="n"/>
     </row>
     <row r="155" ht="42" customHeight="1">
       <c r="A155" s="9" t="n">
@@ -7613,6 +7784,7 @@
       <c r="N155" s="9" t="n"/>
       <c r="O155" s="9" t="n"/>
       <c r="P155" s="9" t="n"/>
+      <c r="Q155" s="9" t="n"/>
     </row>
     <row r="156" ht="42" customHeight="1">
       <c r="A156" s="7" t="n">
@@ -7657,6 +7829,7 @@
       <c r="N156" s="9" t="n"/>
       <c r="O156" s="9" t="n"/>
       <c r="P156" s="9" t="n"/>
+      <c r="Q156" s="9" t="n"/>
     </row>
     <row r="157" ht="42" customHeight="1">
       <c r="A157" s="9" t="n">
@@ -7705,6 +7878,7 @@
       <c r="N157" s="9" t="n"/>
       <c r="O157" s="9" t="n"/>
       <c r="P157" s="9" t="n"/>
+      <c r="Q157" s="9" t="n"/>
     </row>
     <row r="158" ht="42" customHeight="1">
       <c r="A158" s="7" t="n">
@@ -7749,6 +7923,7 @@
       <c r="N158" s="9" t="n"/>
       <c r="O158" s="9" t="n"/>
       <c r="P158" s="9" t="n"/>
+      <c r="Q158" s="9" t="n"/>
     </row>
     <row r="159" ht="42" customHeight="1">
       <c r="A159" s="9" t="n">
@@ -7793,6 +7968,7 @@
       <c r="N159" s="9" t="n"/>
       <c r="O159" s="9" t="n"/>
       <c r="P159" s="9" t="n"/>
+      <c r="Q159" s="9" t="n"/>
     </row>
     <row r="160" ht="42" customHeight="1">
       <c r="A160" s="7" t="n">
@@ -7837,6 +8013,7 @@
       <c r="N160" s="9" t="n"/>
       <c r="O160" s="9" t="n"/>
       <c r="P160" s="9" t="n"/>
+      <c r="Q160" s="9" t="n"/>
     </row>
     <row r="161" ht="42" customHeight="1">
       <c r="A161" s="9" t="n">
@@ -7881,6 +8058,7 @@
       <c r="N161" s="9" t="n"/>
       <c r="O161" s="9" t="n"/>
       <c r="P161" s="9" t="n"/>
+      <c r="Q161" s="9" t="n"/>
     </row>
     <row r="162" ht="42" customHeight="1">
       <c r="A162" s="7" t="n">
@@ -7925,6 +8103,7 @@
       <c r="N162" s="9" t="n"/>
       <c r="O162" s="9" t="n"/>
       <c r="P162" s="9" t="n"/>
+      <c r="Q162" s="9" t="n"/>
     </row>
     <row r="163" ht="42" customHeight="1">
       <c r="A163" s="9" t="n">
@@ -7969,6 +8148,7 @@
       <c r="N163" s="9" t="n"/>
       <c r="O163" s="9" t="n"/>
       <c r="P163" s="9" t="n"/>
+      <c r="Q163" s="9" t="n"/>
     </row>
     <row r="164" ht="42" customHeight="1">
       <c r="A164" s="7" t="n">
@@ -8017,6 +8197,7 @@
       <c r="N164" s="9" t="n"/>
       <c r="O164" s="9" t="n"/>
       <c r="P164" s="9" t="n"/>
+      <c r="Q164" s="9" t="n"/>
     </row>
     <row r="165" ht="42" customHeight="1">
       <c r="A165" s="9" t="n">
@@ -8065,6 +8246,7 @@
       <c r="N165" s="9" t="n"/>
       <c r="O165" s="9" t="n"/>
       <c r="P165" s="9" t="n"/>
+      <c r="Q165" s="9" t="n"/>
     </row>
     <row r="166" ht="42" customHeight="1">
       <c r="A166" s="7" t="n">
@@ -8109,6 +8291,7 @@
       <c r="N166" s="9" t="n"/>
       <c r="O166" s="9" t="n"/>
       <c r="P166" s="9" t="n"/>
+      <c r="Q166" s="9" t="n"/>
     </row>
     <row r="167" ht="42" customHeight="1">
       <c r="A167" s="9" t="n">
@@ -8153,6 +8336,7 @@
       <c r="N167" s="9" t="n"/>
       <c r="O167" s="9" t="n"/>
       <c r="P167" s="9" t="n"/>
+      <c r="Q167" s="9" t="n"/>
     </row>
     <row r="168" ht="42" customHeight="1">
       <c r="A168" s="7" t="n">
@@ -8197,6 +8381,7 @@
       <c r="N168" s="9" t="n"/>
       <c r="O168" s="9" t="n"/>
       <c r="P168" s="9" t="n"/>
+      <c r="Q168" s="9" t="n"/>
     </row>
     <row r="169" ht="42" customHeight="1">
       <c r="A169" s="9" t="n">
@@ -8241,6 +8426,7 @@
       <c r="N169" s="9" t="n"/>
       <c r="O169" s="9" t="n"/>
       <c r="P169" s="9" t="n"/>
+      <c r="Q169" s="9" t="n"/>
     </row>
     <row r="170" ht="42" customHeight="1">
       <c r="A170" s="7" t="n">
@@ -8285,6 +8471,7 @@
       <c r="N170" s="9" t="n"/>
       <c r="O170" s="9" t="n"/>
       <c r="P170" s="9" t="n"/>
+      <c r="Q170" s="9" t="n"/>
     </row>
     <row r="171" ht="42" customHeight="1">
       <c r="A171" s="9" t="n">
@@ -8329,6 +8516,7 @@
       <c r="N171" s="9" t="n"/>
       <c r="O171" s="9" t="n"/>
       <c r="P171" s="9" t="n"/>
+      <c r="Q171" s="9" t="n"/>
     </row>
     <row r="172" ht="42" customHeight="1">
       <c r="A172" s="7" t="n">
@@ -8373,6 +8561,7 @@
       <c r="N172" s="9" t="n"/>
       <c r="O172" s="9" t="n"/>
       <c r="P172" s="9" t="n"/>
+      <c r="Q172" s="9" t="n"/>
     </row>
     <row r="173" ht="42" customHeight="1">
       <c r="A173" s="9" t="n">
@@ -8421,6 +8610,7 @@
       <c r="N173" s="9" t="n"/>
       <c r="O173" s="9" t="n"/>
       <c r="P173" s="9" t="n"/>
+      <c r="Q173" s="9" t="n"/>
     </row>
     <row r="174" ht="42" customHeight="1">
       <c r="A174" s="7" t="n">
@@ -8465,6 +8655,7 @@
       <c r="N174" s="9" t="n"/>
       <c r="O174" s="9" t="n"/>
       <c r="P174" s="9" t="n"/>
+      <c r="Q174" s="9" t="n"/>
     </row>
     <row r="175" ht="42" customHeight="1">
       <c r="A175" s="9" t="n">
@@ -8509,6 +8700,7 @@
       <c r="N175" s="9" t="n"/>
       <c r="O175" s="9" t="n"/>
       <c r="P175" s="9" t="n"/>
+      <c r="Q175" s="9" t="n"/>
     </row>
     <row r="176" ht="42" customHeight="1">
       <c r="A176" s="7" t="n">
@@ -8553,6 +8745,7 @@
       <c r="N176" s="9" t="n"/>
       <c r="O176" s="9" t="n"/>
       <c r="P176" s="9" t="n"/>
+      <c r="Q176" s="9" t="n"/>
     </row>
     <row r="177" ht="42" customHeight="1">
       <c r="A177" s="9" t="n">
@@ -8597,6 +8790,7 @@
       <c r="N177" s="9" t="n"/>
       <c r="O177" s="9" t="n"/>
       <c r="P177" s="9" t="n"/>
+      <c r="Q177" s="9" t="n"/>
     </row>
     <row r="178" ht="42" customHeight="1">
       <c r="A178" s="7" t="n">
@@ -8641,6 +8835,7 @@
       <c r="N178" s="9" t="n"/>
       <c r="O178" s="9" t="n"/>
       <c r="P178" s="9" t="n"/>
+      <c r="Q178" s="9" t="n"/>
     </row>
     <row r="179" ht="42" customHeight="1">
       <c r="A179" s="9" t="n">
@@ -8685,6 +8880,7 @@
       <c r="N179" s="9" t="n"/>
       <c r="O179" s="9" t="n"/>
       <c r="P179" s="9" t="n"/>
+      <c r="Q179" s="9" t="n"/>
     </row>
     <row r="180" ht="42" customHeight="1">
       <c r="A180" s="7" t="n">
@@ -8729,6 +8925,7 @@
       <c r="N180" s="9" t="n"/>
       <c r="O180" s="9" t="n"/>
       <c r="P180" s="9" t="n"/>
+      <c r="Q180" s="9" t="n"/>
     </row>
     <row r="181" ht="42" customHeight="1">
       <c r="A181" s="9" t="n">
@@ -8773,6 +8970,7 @@
       <c r="N181" s="9" t="n"/>
       <c r="O181" s="9" t="n"/>
       <c r="P181" s="9" t="n"/>
+      <c r="Q181" s="9" t="n"/>
     </row>
     <row r="182" ht="42" customHeight="1">
       <c r="A182" s="7" t="n">
@@ -8821,6 +9019,7 @@
       <c r="N182" s="9" t="n"/>
       <c r="O182" s="9" t="n"/>
       <c r="P182" s="9" t="n"/>
+      <c r="Q182" s="9" t="n"/>
     </row>
     <row r="183" ht="42" customHeight="1">
       <c r="A183" s="9" t="n">
@@ -8865,6 +9064,7 @@
       <c r="N183" s="9" t="n"/>
       <c r="O183" s="9" t="n"/>
       <c r="P183" s="9" t="n"/>
+      <c r="Q183" s="9" t="n"/>
     </row>
     <row r="184" ht="42" customHeight="1">
       <c r="A184" s="7" t="n">
@@ -8909,6 +9109,7 @@
       <c r="N184" s="9" t="n"/>
       <c r="O184" s="9" t="n"/>
       <c r="P184" s="9" t="n"/>
+      <c r="Q184" s="9" t="n"/>
     </row>
     <row r="185" ht="42" customHeight="1">
       <c r="A185" s="9" t="n">
@@ -8957,6 +9158,7 @@
       <c r="N185" s="9" t="n"/>
       <c r="O185" s="9" t="n"/>
       <c r="P185" s="9" t="n"/>
+      <c r="Q185" s="9" t="n"/>
     </row>
     <row r="186" ht="42" customHeight="1">
       <c r="A186" s="7" t="n">
@@ -9001,6 +9203,7 @@
       <c r="N186" s="9" t="n"/>
       <c r="O186" s="9" t="n"/>
       <c r="P186" s="9" t="n"/>
+      <c r="Q186" s="9" t="n"/>
     </row>
     <row r="187" ht="42" customHeight="1">
       <c r="A187" s="9" t="n">
@@ -9045,6 +9248,7 @@
       <c r="N187" s="9" t="n"/>
       <c r="O187" s="9" t="n"/>
       <c r="P187" s="9" t="n"/>
+      <c r="Q187" s="9" t="n"/>
     </row>
     <row r="188" ht="42" customHeight="1">
       <c r="A188" s="7" t="n">
@@ -9089,6 +9293,7 @@
       <c r="N188" s="9" t="n"/>
       <c r="O188" s="9" t="n"/>
       <c r="P188" s="9" t="n"/>
+      <c r="Q188" s="9" t="n"/>
     </row>
     <row r="189" ht="42" customHeight="1">
       <c r="A189" s="9" t="n">
@@ -9133,6 +9338,7 @@
       <c r="N189" s="9" t="n"/>
       <c r="O189" s="9" t="n"/>
       <c r="P189" s="9" t="n"/>
+      <c r="Q189" s="9" t="n"/>
     </row>
     <row r="190" ht="42" customHeight="1">
       <c r="A190" s="7" t="n">
@@ -9177,6 +9383,7 @@
       <c r="N190" s="9" t="n"/>
       <c r="O190" s="9" t="n"/>
       <c r="P190" s="9" t="n"/>
+      <c r="Q190" s="9" t="n"/>
     </row>
     <row r="191" ht="42" customHeight="1">
       <c r="A191" s="9" t="n">
@@ -9221,6 +9428,7 @@
       <c r="N191" s="9" t="n"/>
       <c r="O191" s="9" t="n"/>
       <c r="P191" s="9" t="n"/>
+      <c r="Q191" s="9" t="n"/>
     </row>
     <row r="192" ht="42" customHeight="1">
       <c r="A192" s="7" t="n">
@@ -9265,6 +9473,7 @@
       <c r="N192" s="9" t="n"/>
       <c r="O192" s="9" t="n"/>
       <c r="P192" s="9" t="n"/>
+      <c r="Q192" s="9" t="n"/>
     </row>
     <row r="193" ht="42" customHeight="1">
       <c r="A193" s="9" t="n">
@@ -9309,6 +9518,7 @@
       <c r="N193" s="9" t="n"/>
       <c r="O193" s="9" t="n"/>
       <c r="P193" s="9" t="n"/>
+      <c r="Q193" s="9" t="n"/>
     </row>
     <row r="194" ht="42" customHeight="1">
       <c r="A194" s="7" t="n">
@@ -9353,6 +9563,7 @@
       <c r="N194" s="9" t="n"/>
       <c r="O194" s="9" t="n"/>
       <c r="P194" s="9" t="n"/>
+      <c r="Q194" s="9" t="n"/>
     </row>
     <row r="195" ht="42" customHeight="1">
       <c r="A195" s="9" t="n">
@@ -9397,6 +9608,7 @@
       <c r="N195" s="9" t="n"/>
       <c r="O195" s="9" t="n"/>
       <c r="P195" s="9" t="n"/>
+      <c r="Q195" s="9" t="n"/>
     </row>
     <row r="196" ht="42" customHeight="1">
       <c r="A196" s="7" t="n">
@@ -9441,6 +9653,7 @@
       <c r="N196" s="9" t="n"/>
       <c r="O196" s="9" t="n"/>
       <c r="P196" s="9" t="n"/>
+      <c r="Q196" s="9" t="n"/>
     </row>
     <row r="197" ht="42" customHeight="1">
       <c r="A197" s="9" t="n">
@@ -9489,6 +9702,7 @@
       <c r="N197" s="9" t="n"/>
       <c r="O197" s="9" t="n"/>
       <c r="P197" s="9" t="n"/>
+      <c r="Q197" s="9" t="n"/>
     </row>
     <row r="198" ht="42" customHeight="1">
       <c r="A198" s="7" t="n">
@@ -9537,6 +9751,7 @@
       <c r="N198" s="9" t="n"/>
       <c r="O198" s="9" t="n"/>
       <c r="P198" s="9" t="n"/>
+      <c r="Q198" s="9" t="n"/>
     </row>
     <row r="199" ht="42" customHeight="1">
       <c r="A199" s="9" t="n">
@@ -9585,6 +9800,7 @@
       <c r="N199" s="9" t="n"/>
       <c r="O199" s="9" t="n"/>
       <c r="P199" s="9" t="n"/>
+      <c r="Q199" s="9" t="n"/>
     </row>
     <row r="200" ht="42" customHeight="1">
       <c r="A200" s="7" t="n">
@@ -9629,6 +9845,7 @@
       <c r="N200" s="9" t="n"/>
       <c r="O200" s="9" t="n"/>
       <c r="P200" s="9" t="n"/>
+      <c r="Q200" s="9" t="n"/>
     </row>
     <row r="201" ht="42" customHeight="1">
       <c r="A201" s="9" t="n">
@@ -9677,6 +9894,7 @@
       <c r="N201" s="9" t="n"/>
       <c r="O201" s="9" t="n"/>
       <c r="P201" s="9" t="n"/>
+      <c r="Q201" s="9" t="n"/>
     </row>
     <row r="202" ht="42" customHeight="1">
       <c r="A202" s="7" t="n">
@@ -9721,6 +9939,7 @@
       <c r="N202" s="9" t="n"/>
       <c r="O202" s="9" t="n"/>
       <c r="P202" s="9" t="n"/>
+      <c r="Q202" s="9" t="n"/>
     </row>
     <row r="203" ht="42" customHeight="1">
       <c r="A203" s="9" t="n">
@@ -9769,6 +9988,7 @@
       <c r="N203" s="9" t="n"/>
       <c r="O203" s="9" t="n"/>
       <c r="P203" s="9" t="n"/>
+      <c r="Q203" s="9" t="n"/>
     </row>
     <row r="204" ht="42" customHeight="1">
       <c r="A204" s="7" t="n">
@@ -9813,6 +10033,7 @@
       <c r="N204" s="9" t="n"/>
       <c r="O204" s="9" t="n"/>
       <c r="P204" s="9" t="n"/>
+      <c r="Q204" s="9" t="n"/>
     </row>
     <row r="205" ht="42" customHeight="1">
       <c r="A205" s="9" t="n">
@@ -9857,6 +10078,7 @@
       <c r="N205" s="9" t="n"/>
       <c r="O205" s="9" t="n"/>
       <c r="P205" s="9" t="n"/>
+      <c r="Q205" s="9" t="n"/>
     </row>
     <row r="206" ht="42" customHeight="1">
       <c r="A206" s="7" t="n">
@@ -9901,6 +10123,7 @@
       <c r="N206" s="9" t="n"/>
       <c r="O206" s="9" t="n"/>
       <c r="P206" s="9" t="n"/>
+      <c r="Q206" s="9" t="n"/>
     </row>
     <row r="207" ht="42" customHeight="1">
       <c r="A207" s="9" t="n">
@@ -9945,6 +10168,7 @@
       <c r="N207" s="9" t="n"/>
       <c r="O207" s="9" t="n"/>
       <c r="P207" s="9" t="n"/>
+      <c r="Q207" s="9" t="n"/>
     </row>
     <row r="208" ht="42" customHeight="1">
       <c r="A208" s="7" t="n">
@@ -9989,6 +10213,7 @@
       <c r="N208" s="9" t="n"/>
       <c r="O208" s="9" t="n"/>
       <c r="P208" s="9" t="n"/>
+      <c r="Q208" s="9" t="n"/>
     </row>
     <row r="209" ht="42" customHeight="1">
       <c r="A209" s="9" t="n">
@@ -10033,6 +10258,7 @@
       <c r="N209" s="9" t="n"/>
       <c r="O209" s="9" t="n"/>
       <c r="P209" s="9" t="n"/>
+      <c r="Q209" s="9" t="n"/>
     </row>
     <row r="210" ht="42" customHeight="1">
       <c r="A210" s="7" t="n">
@@ -10077,6 +10303,7 @@
       <c r="N210" s="9" t="n"/>
       <c r="O210" s="9" t="n"/>
       <c r="P210" s="9" t="n"/>
+      <c r="Q210" s="9" t="n"/>
     </row>
     <row r="211" ht="42" customHeight="1">
       <c r="A211" s="9" t="n">
@@ -10121,6 +10348,7 @@
       <c r="N211" s="9" t="n"/>
       <c r="O211" s="9" t="n"/>
       <c r="P211" s="9" t="n"/>
+      <c r="Q211" s="9" t="n"/>
     </row>
     <row r="212" ht="42" customHeight="1">
       <c r="A212" s="7" t="n">
@@ -10165,6 +10393,7 @@
       <c r="N212" s="9" t="n"/>
       <c r="O212" s="9" t="n"/>
       <c r="P212" s="9" t="n"/>
+      <c r="Q212" s="9" t="n"/>
     </row>
     <row r="213" ht="42" customHeight="1">
       <c r="A213" s="9" t="n">
@@ -10213,6 +10442,7 @@
       <c r="N213" s="9" t="n"/>
       <c r="O213" s="9" t="n"/>
       <c r="P213" s="9" t="n"/>
+      <c r="Q213" s="9" t="n"/>
     </row>
     <row r="214" ht="42" customHeight="1">
       <c r="A214" s="7" t="n">
@@ -10257,6 +10487,7 @@
       <c r="N214" s="9" t="n"/>
       <c r="O214" s="9" t="n"/>
       <c r="P214" s="9" t="n"/>
+      <c r="Q214" s="9" t="n"/>
     </row>
     <row r="215" ht="42" customHeight="1">
       <c r="A215" s="9" t="n">
@@ -10305,6 +10536,7 @@
       <c r="N215" s="9" t="n"/>
       <c r="O215" s="9" t="n"/>
       <c r="P215" s="9" t="n"/>
+      <c r="Q215" s="9" t="n"/>
     </row>
     <row r="216" ht="42" customHeight="1">
       <c r="A216" s="7" t="n">
@@ -10349,6 +10581,7 @@
       <c r="N216" s="9" t="n"/>
       <c r="O216" s="9" t="n"/>
       <c r="P216" s="9" t="n"/>
+      <c r="Q216" s="9" t="n"/>
     </row>
     <row r="217" ht="42" customHeight="1">
       <c r="A217" s="9" t="n">
@@ -10397,6 +10630,7 @@
       <c r="N217" s="9" t="n"/>
       <c r="O217" s="9" t="n"/>
       <c r="P217" s="9" t="n"/>
+      <c r="Q217" s="9" t="n"/>
     </row>
     <row r="218" ht="42" customHeight="1">
       <c r="A218" s="7" t="n">
@@ -10441,6 +10675,7 @@
       <c r="N218" s="9" t="n"/>
       <c r="O218" s="9" t="n"/>
       <c r="P218" s="9" t="n"/>
+      <c r="Q218" s="9" t="n"/>
     </row>
     <row r="219" ht="42" customHeight="1">
       <c r="A219" s="9" t="n">
@@ -10485,6 +10720,7 @@
       <c r="N219" s="9" t="n"/>
       <c r="O219" s="9" t="n"/>
       <c r="P219" s="9" t="n"/>
+      <c r="Q219" s="9" t="n"/>
     </row>
     <row r="220" ht="42" customHeight="1">
       <c r="A220" s="7" t="n">
@@ -10533,6 +10769,7 @@
       <c r="N220" s="9" t="n"/>
       <c r="O220" s="9" t="n"/>
       <c r="P220" s="9" t="n"/>
+      <c r="Q220" s="9" t="n"/>
     </row>
     <row r="221" ht="42" customHeight="1">
       <c r="A221" s="9" t="n">
@@ -10577,6 +10814,7 @@
       <c r="N221" s="9" t="n"/>
       <c r="O221" s="9" t="n"/>
       <c r="P221" s="9" t="n"/>
+      <c r="Q221" s="9" t="n"/>
     </row>
     <row r="222" ht="42" customHeight="1">
       <c r="A222" s="7" t="n">
@@ -10621,6 +10859,7 @@
       <c r="N222" s="9" t="n"/>
       <c r="O222" s="9" t="n"/>
       <c r="P222" s="9" t="n"/>
+      <c r="Q222" s="9" t="n"/>
     </row>
     <row r="223" ht="42" customHeight="1">
       <c r="A223" s="9" t="n">
@@ -10665,6 +10904,7 @@
       <c r="N223" s="9" t="n"/>
       <c r="O223" s="9" t="n"/>
       <c r="P223" s="9" t="n"/>
+      <c r="Q223" s="9" t="n"/>
     </row>
     <row r="224" ht="42" customHeight="1">
       <c r="A224" s="7" t="n">
@@ -10709,6 +10949,7 @@
       <c r="N224" s="9" t="n"/>
       <c r="O224" s="9" t="n"/>
       <c r="P224" s="9" t="n"/>
+      <c r="Q224" s="9" t="n"/>
     </row>
     <row r="225" ht="42" customHeight="1">
       <c r="A225" s="9" t="n">
@@ -10753,6 +10994,7 @@
       <c r="N225" s="9" t="n"/>
       <c r="O225" s="9" t="n"/>
       <c r="P225" s="9" t="n"/>
+      <c r="Q225" s="9" t="n"/>
     </row>
     <row r="226" ht="42" customHeight="1">
       <c r="A226" s="7" t="n">
@@ -10801,6 +11043,7 @@
       <c r="N226" s="9" t="n"/>
       <c r="O226" s="9" t="n"/>
       <c r="P226" s="9" t="n"/>
+      <c r="Q226" s="9" t="n"/>
     </row>
     <row r="227" ht="42" customHeight="1">
       <c r="A227" s="9" t="n">
@@ -10849,6 +11092,7 @@
       <c r="N227" s="9" t="n"/>
       <c r="O227" s="9" t="n"/>
       <c r="P227" s="9" t="n"/>
+      <c r="Q227" s="9" t="n"/>
     </row>
     <row r="228" ht="42" customHeight="1">
       <c r="A228" s="7" t="n">
@@ -10897,6 +11141,7 @@
       <c r="N228" s="9" t="n"/>
       <c r="O228" s="9" t="n"/>
       <c r="P228" s="9" t="n"/>
+      <c r="Q228" s="9" t="n"/>
     </row>
     <row r="229" ht="42" customHeight="1">
       <c r="A229" s="9" t="n">
@@ -10941,6 +11186,7 @@
       <c r="N229" s="9" t="n"/>
       <c r="O229" s="9" t="n"/>
       <c r="P229" s="9" t="n"/>
+      <c r="Q229" s="9" t="n"/>
     </row>
     <row r="230" ht="42" customHeight="1">
       <c r="A230" s="7" t="n">
@@ -10985,6 +11231,7 @@
       <c r="N230" s="9" t="n"/>
       <c r="O230" s="9" t="n"/>
       <c r="P230" s="9" t="n"/>
+      <c r="Q230" s="9" t="n"/>
     </row>
     <row r="231" ht="42" customHeight="1">
       <c r="A231" s="9" t="n">
@@ -11033,6 +11280,7 @@
       <c r="N231" s="9" t="n"/>
       <c r="O231" s="9" t="n"/>
       <c r="P231" s="9" t="n"/>
+      <c r="Q231" s="9" t="n"/>
     </row>
     <row r="232" ht="42" customHeight="1">
       <c r="A232" s="7" t="n">
@@ -11081,6 +11329,7 @@
       <c r="N232" s="9" t="n"/>
       <c r="O232" s="9" t="n"/>
       <c r="P232" s="9" t="n"/>
+      <c r="Q232" s="9" t="n"/>
     </row>
     <row r="233" ht="42" customHeight="1">
       <c r="A233" s="9" t="n">
@@ -11125,6 +11374,7 @@
       <c r="N233" s="9" t="n"/>
       <c r="O233" s="9" t="n"/>
       <c r="P233" s="9" t="n"/>
+      <c r="Q233" s="9" t="n"/>
     </row>
     <row r="234" ht="42" customHeight="1">
       <c r="A234" s="7" t="n">
@@ -11169,6 +11419,7 @@
       <c r="N234" s="9" t="n"/>
       <c r="O234" s="9" t="n"/>
       <c r="P234" s="9" t="n"/>
+      <c r="Q234" s="9" t="n"/>
     </row>
     <row r="235" ht="42" customHeight="1">
       <c r="A235" s="9" t="n">
@@ -11217,6 +11468,7 @@
       <c r="N235" s="9" t="n"/>
       <c r="O235" s="9" t="n"/>
       <c r="P235" s="9" t="n"/>
+      <c r="Q235" s="9" t="n"/>
     </row>
     <row r="236" ht="42" customHeight="1">
       <c r="A236" s="7" t="n">
@@ -11265,6 +11517,7 @@
       <c r="N236" s="9" t="n"/>
       <c r="O236" s="9" t="n"/>
       <c r="P236" s="9" t="n"/>
+      <c r="Q236" s="9" t="n"/>
     </row>
     <row r="237" ht="42" customHeight="1">
       <c r="A237" s="9" t="n">
@@ -11313,6 +11566,7 @@
       <c r="N237" s="9" t="n"/>
       <c r="O237" s="9" t="n"/>
       <c r="P237" s="9" t="n"/>
+      <c r="Q237" s="9" t="n"/>
     </row>
     <row r="238" ht="42" customHeight="1">
       <c r="A238" s="7" t="n">
@@ -11361,6 +11615,7 @@
       <c r="N238" s="9" t="n"/>
       <c r="O238" s="9" t="n"/>
       <c r="P238" s="9" t="n"/>
+      <c r="Q238" s="9" t="n"/>
     </row>
     <row r="239" ht="42" customHeight="1">
       <c r="A239" s="9" t="n">
@@ -11405,6 +11660,7 @@
       <c r="N239" s="9" t="n"/>
       <c r="O239" s="9" t="n"/>
       <c r="P239" s="9" t="n"/>
+      <c r="Q239" s="9" t="n"/>
     </row>
     <row r="240" ht="42" customHeight="1">
       <c r="A240" s="7" t="n">
@@ -11449,6 +11705,7 @@
       <c r="N240" s="9" t="n"/>
       <c r="O240" s="9" t="n"/>
       <c r="P240" s="9" t="n"/>
+      <c r="Q240" s="9" t="n"/>
     </row>
     <row r="241" ht="42" customHeight="1">
       <c r="A241" s="9" t="n">
@@ -11493,6 +11750,7 @@
       <c r="N241" s="9" t="n"/>
       <c r="O241" s="9" t="n"/>
       <c r="P241" s="9" t="n"/>
+      <c r="Q241" s="9" t="n"/>
     </row>
     <row r="242" ht="42" customHeight="1">
       <c r="A242" s="7" t="n">
@@ -11541,6 +11799,7 @@
       <c r="N242" s="9" t="n"/>
       <c r="O242" s="9" t="n"/>
       <c r="P242" s="9" t="n"/>
+      <c r="Q242" s="9" t="n"/>
     </row>
     <row r="243" ht="42" customHeight="1">
       <c r="A243" s="9" t="n">
@@ -11585,6 +11844,7 @@
       <c r="N243" s="9" t="n"/>
       <c r="O243" s="9" t="n"/>
       <c r="P243" s="9" t="n"/>
+      <c r="Q243" s="9" t="n"/>
     </row>
     <row r="244" ht="42" customHeight="1">
       <c r="A244" s="7" t="n">
@@ -11633,6 +11893,7 @@
       <c r="N244" s="9" t="n"/>
       <c r="O244" s="9" t="n"/>
       <c r="P244" s="9" t="n"/>
+      <c r="Q244" s="9" t="n"/>
     </row>
     <row r="245" ht="42" customHeight="1">
       <c r="A245" s="9" t="n">
@@ -11677,6 +11938,7 @@
       <c r="N245" s="9" t="n"/>
       <c r="O245" s="9" t="n"/>
       <c r="P245" s="9" t="n"/>
+      <c r="Q245" s="9" t="n"/>
     </row>
     <row r="246" ht="42" customHeight="1">
       <c r="A246" s="7" t="n">
@@ -11721,6 +11983,7 @@
       <c r="N246" s="9" t="n"/>
       <c r="O246" s="9" t="n"/>
       <c r="P246" s="9" t="n"/>
+      <c r="Q246" s="9" t="n"/>
     </row>
     <row r="247" ht="42" customHeight="1">
       <c r="A247" s="9" t="n">
@@ -11765,6 +12028,7 @@
       <c r="N247" s="9" t="n"/>
       <c r="O247" s="9" t="n"/>
       <c r="P247" s="9" t="n"/>
+      <c r="Q247" s="9" t="n"/>
     </row>
     <row r="248" ht="42" customHeight="1">
       <c r="A248" s="7" t="n">
@@ -11809,6 +12073,7 @@
       <c r="N248" s="9" t="n"/>
       <c r="O248" s="9" t="n"/>
       <c r="P248" s="9" t="n"/>
+      <c r="Q248" s="9" t="n"/>
     </row>
     <row r="249" ht="42" customHeight="1">
       <c r="A249" s="9" t="n">
@@ -11857,6 +12122,7 @@
       <c r="N249" s="9" t="n"/>
       <c r="O249" s="9" t="n"/>
       <c r="P249" s="9" t="n"/>
+      <c r="Q249" s="9" t="n"/>
     </row>
     <row r="250" ht="42" customHeight="1">
       <c r="A250" s="7" t="n">
@@ -11901,6 +12167,7 @@
       <c r="N250" s="9" t="n"/>
       <c r="O250" s="9" t="n"/>
       <c r="P250" s="9" t="n"/>
+      <c r="Q250" s="9" t="n"/>
     </row>
     <row r="251" ht="42" customHeight="1">
       <c r="A251" s="9" t="n">
@@ -11949,6 +12216,7 @@
       <c r="N251" s="9" t="n"/>
       <c r="O251" s="9" t="n"/>
       <c r="P251" s="9" t="n"/>
+      <c r="Q251" s="9" t="n"/>
     </row>
     <row r="252" ht="42" customHeight="1">
       <c r="A252" s="7" t="n">
@@ -11993,6 +12261,7 @@
       <c r="N252" s="9" t="n"/>
       <c r="O252" s="9" t="n"/>
       <c r="P252" s="9" t="n"/>
+      <c r="Q252" s="9" t="n"/>
     </row>
     <row r="253" ht="42" customHeight="1">
       <c r="A253" s="9" t="n">
@@ -12041,6 +12310,7 @@
       <c r="N253" s="9" t="n"/>
       <c r="O253" s="9" t="n"/>
       <c r="P253" s="9" t="n"/>
+      <c r="Q253" s="9" t="n"/>
     </row>
     <row r="254" ht="42" customHeight="1">
       <c r="A254" s="7" t="n">
@@ -12085,6 +12355,7 @@
       <c r="N254" s="9" t="n"/>
       <c r="O254" s="9" t="n"/>
       <c r="P254" s="9" t="n"/>
+      <c r="Q254" s="9" t="n"/>
     </row>
     <row r="255" ht="42" customHeight="1">
       <c r="A255" s="9" t="n">
@@ -12129,6 +12400,7 @@
       <c r="N255" s="9" t="n"/>
       <c r="O255" s="9" t="n"/>
       <c r="P255" s="9" t="n"/>
+      <c r="Q255" s="9" t="n"/>
     </row>
     <row r="256" ht="42" customHeight="1">
       <c r="A256" s="7" t="n">
@@ -12173,6 +12445,7 @@
       <c r="N256" s="9" t="n"/>
       <c r="O256" s="9" t="n"/>
       <c r="P256" s="9" t="n"/>
+      <c r="Q256" s="9" t="n"/>
     </row>
     <row r="257" ht="42" customHeight="1">
       <c r="A257" s="9" t="n">
@@ -12217,6 +12490,7 @@
       <c r="N257" s="9" t="n"/>
       <c r="O257" s="9" t="n"/>
       <c r="P257" s="9" t="n"/>
+      <c r="Q257" s="9" t="n"/>
     </row>
     <row r="258" ht="42" customHeight="1">
       <c r="A258" s="7" t="n">
@@ -12261,6 +12535,7 @@
       <c r="N258" s="9" t="n"/>
       <c r="O258" s="9" t="n"/>
       <c r="P258" s="9" t="n"/>
+      <c r="Q258" s="9" t="n"/>
     </row>
     <row r="259" ht="42" customHeight="1">
       <c r="A259" s="9" t="n">
@@ -12305,6 +12580,7 @@
       <c r="N259" s="9" t="n"/>
       <c r="O259" s="9" t="n"/>
       <c r="P259" s="9" t="n"/>
+      <c r="Q259" s="9" t="n"/>
     </row>
     <row r="260" ht="42" customHeight="1">
       <c r="A260" s="7" t="n">
@@ -12349,6 +12625,7 @@
       <c r="N260" s="9" t="n"/>
       <c r="O260" s="9" t="n"/>
       <c r="P260" s="9" t="n"/>
+      <c r="Q260" s="9" t="n"/>
     </row>
     <row r="261" ht="42" customHeight="1">
       <c r="A261" s="9" t="n">
@@ -12397,6 +12674,7 @@
       <c r="N261" s="9" t="n"/>
       <c r="O261" s="9" t="n"/>
       <c r="P261" s="9" t="n"/>
+      <c r="Q261" s="9" t="n"/>
     </row>
     <row r="262" ht="42" customHeight="1">
       <c r="A262" s="7" t="n">
@@ -12441,6 +12719,7 @@
       <c r="N262" s="9" t="n"/>
       <c r="O262" s="9" t="n"/>
       <c r="P262" s="9" t="n"/>
+      <c r="Q262" s="9" t="n"/>
     </row>
     <row r="263" ht="42" customHeight="1">
       <c r="A263" s="9" t="n">
@@ -12485,6 +12764,7 @@
       <c r="N263" s="9" t="n"/>
       <c r="O263" s="9" t="n"/>
       <c r="P263" s="9" t="n"/>
+      <c r="Q263" s="9" t="n"/>
     </row>
     <row r="264" ht="42" customHeight="1">
       <c r="A264" s="7" t="n">
@@ -12529,6 +12809,7 @@
       <c r="N264" s="9" t="n"/>
       <c r="O264" s="9" t="n"/>
       <c r="P264" s="9" t="n"/>
+      <c r="Q264" s="9" t="n"/>
     </row>
     <row r="265" ht="42" customHeight="1">
       <c r="A265" s="9" t="n">
@@ -12573,6 +12854,7 @@
       <c r="N265" s="9" t="n"/>
       <c r="O265" s="9" t="n"/>
       <c r="P265" s="9" t="n"/>
+      <c r="Q265" s="9" t="n"/>
     </row>
     <row r="266" ht="42" customHeight="1">
       <c r="A266" s="7" t="n">
@@ -12617,6 +12899,7 @@
       <c r="N266" s="9" t="n"/>
       <c r="O266" s="9" t="n"/>
       <c r="P266" s="9" t="n"/>
+      <c r="Q266" s="9" t="n"/>
     </row>
     <row r="267" ht="42" customHeight="1">
       <c r="A267" s="9" t="n">
@@ -12661,6 +12944,7 @@
       <c r="N267" s="9" t="n"/>
       <c r="O267" s="9" t="n"/>
       <c r="P267" s="9" t="n"/>
+      <c r="Q267" s="9" t="n"/>
     </row>
     <row r="268" ht="42" customHeight="1">
       <c r="A268" s="7" t="n">
@@ -12709,6 +12993,7 @@
       <c r="N268" s="9" t="n"/>
       <c r="O268" s="9" t="n"/>
       <c r="P268" s="9" t="n"/>
+      <c r="Q268" s="9" t="n"/>
     </row>
     <row r="269" ht="42" customHeight="1">
       <c r="A269" s="9" t="n">
@@ -12753,6 +13038,7 @@
       <c r="N269" s="9" t="n"/>
       <c r="O269" s="9" t="n"/>
       <c r="P269" s="9" t="n"/>
+      <c r="Q269" s="9" t="n"/>
     </row>
     <row r="270" ht="42" customHeight="1">
       <c r="A270" s="7" t="n">
@@ -12801,6 +13087,7 @@
       <c r="N270" s="9" t="n"/>
       <c r="O270" s="9" t="n"/>
       <c r="P270" s="9" t="n"/>
+      <c r="Q270" s="9" t="n"/>
     </row>
     <row r="271" ht="42" customHeight="1">
       <c r="A271" s="9" t="n">
@@ -12845,6 +13132,7 @@
       <c r="N271" s="9" t="n"/>
       <c r="O271" s="9" t="n"/>
       <c r="P271" s="9" t="n"/>
+      <c r="Q271" s="9" t="n"/>
     </row>
     <row r="272" ht="42" customHeight="1">
       <c r="A272" s="7" t="n">
@@ -12889,6 +13177,7 @@
       <c r="N272" s="9" t="n"/>
       <c r="O272" s="9" t="n"/>
       <c r="P272" s="9" t="n"/>
+      <c r="Q272" s="9" t="n"/>
     </row>
     <row r="273" ht="42" customHeight="1">
       <c r="A273" s="9" t="n">
@@ -12933,6 +13222,7 @@
       <c r="N273" s="9" t="n"/>
       <c r="O273" s="9" t="n"/>
       <c r="P273" s="9" t="n"/>
+      <c r="Q273" s="9" t="n"/>
     </row>
     <row r="274" ht="42" customHeight="1">
       <c r="A274" s="7" t="n">
@@ -12977,6 +13267,7 @@
       <c r="N274" s="9" t="n"/>
       <c r="O274" s="9" t="n"/>
       <c r="P274" s="9" t="n"/>
+      <c r="Q274" s="9" t="n"/>
     </row>
     <row r="275" ht="42" customHeight="1">
       <c r="A275" s="9" t="n">
@@ -13021,6 +13312,7 @@
       <c r="N275" s="9" t="n"/>
       <c r="O275" s="9" t="n"/>
       <c r="P275" s="9" t="n"/>
+      <c r="Q275" s="9" t="n"/>
     </row>
     <row r="276" ht="42" customHeight="1">
       <c r="A276" s="7" t="n">
@@ -13065,6 +13357,7 @@
       <c r="N276" s="9" t="n"/>
       <c r="O276" s="9" t="n"/>
       <c r="P276" s="9" t="n"/>
+      <c r="Q276" s="9" t="n"/>
     </row>
     <row r="277" ht="42" customHeight="1">
       <c r="A277" s="9" t="n">
@@ -13109,6 +13402,7 @@
       <c r="N277" s="9" t="n"/>
       <c r="O277" s="9" t="n"/>
       <c r="P277" s="9" t="n"/>
+      <c r="Q277" s="9" t="n"/>
     </row>
     <row r="278" ht="42" customHeight="1">
       <c r="A278" s="7" t="n">
@@ -13157,6 +13451,7 @@
       <c r="N278" s="9" t="n"/>
       <c r="O278" s="9" t="n"/>
       <c r="P278" s="9" t="n"/>
+      <c r="Q278" s="9" t="n"/>
     </row>
     <row r="279" ht="42" customHeight="1">
       <c r="A279" s="9" t="n">
@@ -13201,6 +13496,7 @@
       <c r="N279" s="9" t="n"/>
       <c r="O279" s="9" t="n"/>
       <c r="P279" s="9" t="n"/>
+      <c r="Q279" s="9" t="n"/>
     </row>
     <row r="280" ht="42" customHeight="1">
       <c r="A280" s="7" t="n">
@@ -13245,6 +13541,7 @@
       <c r="N280" s="9" t="n"/>
       <c r="O280" s="9" t="n"/>
       <c r="P280" s="9" t="n"/>
+      <c r="Q280" s="9" t="n"/>
     </row>
     <row r="281" ht="42" customHeight="1">
       <c r="A281" s="9" t="n">
@@ -13293,6 +13590,7 @@
       <c r="N281" s="9" t="n"/>
       <c r="O281" s="9" t="n"/>
       <c r="P281" s="9" t="n"/>
+      <c r="Q281" s="9" t="n"/>
     </row>
     <row r="282" ht="42" customHeight="1">
       <c r="A282" s="7" t="n">
@@ -13337,6 +13635,7 @@
       <c r="N282" s="9" t="n"/>
       <c r="O282" s="9" t="n"/>
       <c r="P282" s="9" t="n"/>
+      <c r="Q282" s="9" t="n"/>
     </row>
     <row r="283" ht="42" customHeight="1">
       <c r="A283" s="9" t="n">
@@ -13381,6 +13680,7 @@
       <c r="N283" s="9" t="n"/>
       <c r="O283" s="9" t="n"/>
       <c r="P283" s="9" t="n"/>
+      <c r="Q283" s="9" t="n"/>
     </row>
     <row r="284" ht="42" customHeight="1">
       <c r="A284" s="7" t="n">
@@ -13425,6 +13725,7 @@
       <c r="N284" s="9" t="n"/>
       <c r="O284" s="9" t="n"/>
       <c r="P284" s="9" t="n"/>
+      <c r="Q284" s="9" t="n"/>
     </row>
     <row r="285" ht="42" customHeight="1">
       <c r="A285" s="9" t="n">
@@ -13469,6 +13770,7 @@
       <c r="N285" s="9" t="n"/>
       <c r="O285" s="9" t="n"/>
       <c r="P285" s="9" t="n"/>
+      <c r="Q285" s="9" t="n"/>
     </row>
     <row r="286" ht="42" customHeight="1">
       <c r="A286" s="7" t="n">
@@ -13513,6 +13815,7 @@
       <c r="N286" s="9" t="n"/>
       <c r="O286" s="9" t="n"/>
       <c r="P286" s="9" t="n"/>
+      <c r="Q286" s="9" t="n"/>
     </row>
     <row r="287" ht="42" customHeight="1">
       <c r="A287" s="9" t="n">
@@ -13561,6 +13864,7 @@
       <c r="N287" s="9" t="n"/>
       <c r="O287" s="9" t="n"/>
       <c r="P287" s="9" t="n"/>
+      <c r="Q287" s="9" t="n"/>
     </row>
     <row r="288" ht="42" customHeight="1">
       <c r="A288" s="7" t="n">
@@ -13605,6 +13909,7 @@
       <c r="N288" s="9" t="n"/>
       <c r="O288" s="9" t="n"/>
       <c r="P288" s="9" t="n"/>
+      <c r="Q288" s="9" t="n"/>
     </row>
     <row r="289" ht="42" customHeight="1">
       <c r="A289" s="9" t="n">
@@ -13649,6 +13954,7 @@
       <c r="N289" s="9" t="n"/>
       <c r="O289" s="9" t="n"/>
       <c r="P289" s="9" t="n"/>
+      <c r="Q289" s="9" t="n"/>
     </row>
     <row r="290" ht="42" customHeight="1">
       <c r="A290" s="7" t="n">
@@ -13693,6 +13999,7 @@
       <c r="N290" s="9" t="n"/>
       <c r="O290" s="9" t="n"/>
       <c r="P290" s="9" t="n"/>
+      <c r="Q290" s="9" t="n"/>
     </row>
     <row r="291" ht="42" customHeight="1">
       <c r="A291" s="9" t="n">
@@ -13737,6 +14044,7 @@
       <c r="N291" s="9" t="n"/>
       <c r="O291" s="9" t="n"/>
       <c r="P291" s="9" t="n"/>
+      <c r="Q291" s="9" t="n"/>
     </row>
     <row r="292" ht="42" customHeight="1">
       <c r="A292" s="7" t="n">
@@ -13781,6 +14089,7 @@
       <c r="N292" s="9" t="n"/>
       <c r="O292" s="9" t="n"/>
       <c r="P292" s="9" t="n"/>
+      <c r="Q292" s="9" t="n"/>
     </row>
     <row r="293" ht="42" customHeight="1">
       <c r="A293" s="9" t="n">
@@ -13829,6 +14138,7 @@
       <c r="N293" s="9" t="n"/>
       <c r="O293" s="9" t="n"/>
       <c r="P293" s="9" t="n"/>
+      <c r="Q293" s="9" t="n"/>
     </row>
     <row r="294" ht="42" customHeight="1">
       <c r="A294" s="7" t="n">
@@ -13877,6 +14187,7 @@
       <c r="N294" s="9" t="n"/>
       <c r="O294" s="9" t="n"/>
       <c r="P294" s="9" t="n"/>
+      <c r="Q294" s="9" t="n"/>
     </row>
     <row r="295" ht="42" customHeight="1">
       <c r="A295" s="9" t="n">
@@ -13925,6 +14236,7 @@
       <c r="N295" s="9" t="n"/>
       <c r="O295" s="9" t="n"/>
       <c r="P295" s="9" t="n"/>
+      <c r="Q295" s="9" t="n"/>
     </row>
     <row r="296" ht="42" customHeight="1">
       <c r="A296" s="7" t="n">
@@ -13969,6 +14281,7 @@
       <c r="N296" s="9" t="n"/>
       <c r="O296" s="9" t="n"/>
       <c r="P296" s="9" t="n"/>
+      <c r="Q296" s="9" t="n"/>
     </row>
     <row r="297" ht="42" customHeight="1">
       <c r="A297" s="9" t="n">
@@ -14017,6 +14330,7 @@
       <c r="N297" s="9" t="n"/>
       <c r="O297" s="9" t="n"/>
       <c r="P297" s="9" t="n"/>
+      <c r="Q297" s="9" t="n"/>
     </row>
     <row r="298" ht="42" customHeight="1">
       <c r="A298" s="7" t="n">
@@ -14061,6 +14375,7 @@
       <c r="N298" s="9" t="n"/>
       <c r="O298" s="9" t="n"/>
       <c r="P298" s="9" t="n"/>
+      <c r="Q298" s="9" t="n"/>
     </row>
     <row r="299" ht="42" customHeight="1">
       <c r="A299" s="9" t="n">
@@ -14105,6 +14420,7 @@
       <c r="N299" s="9" t="n"/>
       <c r="O299" s="9" t="n"/>
       <c r="P299" s="9" t="n"/>
+      <c r="Q299" s="9" t="n"/>
     </row>
     <row r="300" ht="42" customHeight="1">
       <c r="A300" s="7" t="n">
@@ -14149,6 +14465,7 @@
       <c r="N300" s="9" t="n"/>
       <c r="O300" s="9" t="n"/>
       <c r="P300" s="9" t="n"/>
+      <c r="Q300" s="9" t="n"/>
     </row>
     <row r="301" ht="42" customHeight="1">
       <c r="A301" s="9" t="n">
@@ -14197,6 +14514,7 @@
       <c r="N301" s="9" t="n"/>
       <c r="O301" s="9" t="n"/>
       <c r="P301" s="9" t="n"/>
+      <c r="Q301" s="9" t="n"/>
     </row>
     <row r="302" ht="42" customHeight="1">
       <c r="A302" s="7" t="n">
@@ -14241,6 +14559,7 @@
       <c r="N302" s="9" t="n"/>
       <c r="O302" s="9" t="n"/>
       <c r="P302" s="9" t="n"/>
+      <c r="Q302" s="9" t="n"/>
     </row>
     <row r="303" ht="42" customHeight="1">
       <c r="A303" s="9" t="n">
@@ -14285,6 +14604,7 @@
       <c r="N303" s="9" t="n"/>
       <c r="O303" s="9" t="n"/>
       <c r="P303" s="9" t="n"/>
+      <c r="Q303" s="9" t="n"/>
     </row>
     <row r="304" ht="42" customHeight="1">
       <c r="A304" s="7" t="n">
@@ -14329,6 +14649,7 @@
       <c r="N304" s="9" t="n"/>
       <c r="O304" s="9" t="n"/>
       <c r="P304" s="9" t="n"/>
+      <c r="Q304" s="9" t="n"/>
     </row>
     <row r="305" ht="42" customHeight="1">
       <c r="A305" s="9" t="n">
@@ -14373,6 +14694,7 @@
       <c r="N305" s="9" t="n"/>
       <c r="O305" s="9" t="n"/>
       <c r="P305" s="9" t="n"/>
+      <c r="Q305" s="9" t="n"/>
     </row>
     <row r="306" ht="42" customHeight="1">
       <c r="A306" s="7" t="n">
@@ -14417,6 +14739,7 @@
       <c r="N306" s="9" t="n"/>
       <c r="O306" s="9" t="n"/>
       <c r="P306" s="9" t="n"/>
+      <c r="Q306" s="9" t="n"/>
     </row>
     <row r="307" ht="42" customHeight="1">
       <c r="A307" s="9" t="n">
@@ -14461,6 +14784,7 @@
       <c r="N307" s="9" t="n"/>
       <c r="O307" s="9" t="n"/>
       <c r="P307" s="9" t="n"/>
+      <c r="Q307" s="9" t="n"/>
     </row>
     <row r="308" ht="42" customHeight="1">
       <c r="A308" s="7" t="n">
@@ -14505,6 +14829,7 @@
       <c r="N308" s="9" t="n"/>
       <c r="O308" s="9" t="n"/>
       <c r="P308" s="9" t="n"/>
+      <c r="Q308" s="9" t="n"/>
     </row>
     <row r="309" ht="42" customHeight="1">
       <c r="A309" s="9" t="n">
@@ -14549,6 +14874,7 @@
       <c r="N309" s="9" t="n"/>
       <c r="O309" s="9" t="n"/>
       <c r="P309" s="9" t="n"/>
+      <c r="Q309" s="9" t="n"/>
     </row>
     <row r="310" ht="42" customHeight="1">
       <c r="A310" s="7" t="n">
@@ -14593,6 +14919,7 @@
       <c r="N310" s="9" t="n"/>
       <c r="O310" s="9" t="n"/>
       <c r="P310" s="9" t="n"/>
+      <c r="Q310" s="9" t="n"/>
     </row>
     <row r="311" ht="42" customHeight="1">
       <c r="A311" s="9" t="n">
@@ -14637,6 +14964,7 @@
       <c r="N311" s="9" t="n"/>
       <c r="O311" s="9" t="n"/>
       <c r="P311" s="9" t="n"/>
+      <c r="Q311" s="9" t="n"/>
     </row>
     <row r="312" ht="42" customHeight="1">
       <c r="A312" s="7" t="n">
@@ -14685,6 +15013,7 @@
       <c r="N312" s="9" t="n"/>
       <c r="O312" s="9" t="n"/>
       <c r="P312" s="9" t="n"/>
+      <c r="Q312" s="9" t="n"/>
     </row>
     <row r="313" ht="42" customHeight="1">
       <c r="A313" s="9" t="n">
@@ -14729,6 +15058,7 @@
       <c r="N313" s="9" t="n"/>
       <c r="O313" s="9" t="n"/>
       <c r="P313" s="9" t="n"/>
+      <c r="Q313" s="9" t="n"/>
     </row>
     <row r="314" ht="42" customHeight="1">
       <c r="A314" s="7" t="n">
@@ -14773,6 +15103,7 @@
       <c r="N314" s="9" t="n"/>
       <c r="O314" s="9" t="n"/>
       <c r="P314" s="9" t="n"/>
+      <c r="Q314" s="9" t="n"/>
     </row>
     <row r="315" ht="42" customHeight="1">
       <c r="A315" s="9" t="n">
@@ -14817,6 +15148,7 @@
       <c r="N315" s="9" t="n"/>
       <c r="O315" s="9" t="n"/>
       <c r="P315" s="9" t="n"/>
+      <c r="Q315" s="9" t="n"/>
     </row>
     <row r="316" ht="42" customHeight="1">
       <c r="A316" s="7" t="n">
@@ -14861,6 +15193,7 @@
       <c r="N316" s="9" t="n"/>
       <c r="O316" s="9" t="n"/>
       <c r="P316" s="9" t="n"/>
+      <c r="Q316" s="9" t="n"/>
     </row>
     <row r="317" ht="42" customHeight="1">
       <c r="A317" s="9" t="n">
@@ -14909,6 +15242,7 @@
       <c r="N317" s="9" t="n"/>
       <c r="O317" s="9" t="n"/>
       <c r="P317" s="9" t="n"/>
+      <c r="Q317" s="9" t="n"/>
     </row>
     <row r="318" ht="42" customHeight="1">
       <c r="A318" s="7" t="n">
@@ -14953,6 +15287,7 @@
       <c r="N318" s="9" t="n"/>
       <c r="O318" s="9" t="n"/>
       <c r="P318" s="9" t="n"/>
+      <c r="Q318" s="9" t="n"/>
     </row>
     <row r="319" ht="42" customHeight="1">
       <c r="A319" s="9" t="n">
@@ -15001,6 +15336,7 @@
       <c r="N319" s="9" t="n"/>
       <c r="O319" s="9" t="n"/>
       <c r="P319" s="9" t="n"/>
+      <c r="Q319" s="9" t="n"/>
     </row>
     <row r="320" ht="42" customHeight="1">
       <c r="A320" s="7" t="n">
@@ -15045,6 +15381,7 @@
       <c r="N320" s="9" t="n"/>
       <c r="O320" s="9" t="n"/>
       <c r="P320" s="9" t="n"/>
+      <c r="Q320" s="9" t="n"/>
     </row>
     <row r="321" ht="42" customHeight="1">
       <c r="A321" s="9" t="n">
@@ -15093,6 +15430,7 @@
       <c r="N321" s="9" t="n"/>
       <c r="O321" s="9" t="n"/>
       <c r="P321" s="9" t="n"/>
+      <c r="Q321" s="9" t="n"/>
     </row>
     <row r="322" ht="42" customHeight="1">
       <c r="A322" s="7" t="n">
@@ -15137,6 +15475,7 @@
       <c r="N322" s="9" t="n"/>
       <c r="O322" s="9" t="n"/>
       <c r="P322" s="9" t="n"/>
+      <c r="Q322" s="9" t="n"/>
     </row>
     <row r="323" ht="42" customHeight="1">
       <c r="A323" s="9" t="n">
@@ -15181,6 +15520,7 @@
       <c r="N323" s="9" t="n"/>
       <c r="O323" s="9" t="n"/>
       <c r="P323" s="9" t="n"/>
+      <c r="Q323" s="9" t="n"/>
     </row>
     <row r="324" ht="42" customHeight="1">
       <c r="A324" s="7" t="n">
@@ -15225,6 +15565,7 @@
       <c r="N324" s="9" t="n"/>
       <c r="O324" s="9" t="n"/>
       <c r="P324" s="9" t="n"/>
+      <c r="Q324" s="9" t="n"/>
     </row>
     <row r="325" ht="42" customHeight="1">
       <c r="A325" s="9" t="n">
@@ -15269,6 +15610,7 @@
       <c r="N325" s="9" t="n"/>
       <c r="O325" s="9" t="n"/>
       <c r="P325" s="9" t="n"/>
+      <c r="Q325" s="9" t="n"/>
     </row>
     <row r="326" ht="42" customHeight="1">
       <c r="A326" s="7" t="n">
@@ -15317,6 +15659,7 @@
       <c r="N326" s="9" t="n"/>
       <c r="O326" s="9" t="n"/>
       <c r="P326" s="9" t="n"/>
+      <c r="Q326" s="9" t="n"/>
     </row>
     <row r="327" ht="42" customHeight="1">
       <c r="A327" s="9" t="n">
@@ -15361,6 +15704,7 @@
       <c r="N327" s="9" t="n"/>
       <c r="O327" s="9" t="n"/>
       <c r="P327" s="9" t="n"/>
+      <c r="Q327" s="9" t="n"/>
     </row>
     <row r="328" ht="42" customHeight="1">
       <c r="A328" s="7" t="n">
@@ -15405,6 +15749,7 @@
       <c r="N328" s="9" t="n"/>
       <c r="O328" s="9" t="n"/>
       <c r="P328" s="9" t="n"/>
+      <c r="Q328" s="9" t="n"/>
     </row>
     <row r="329" ht="42" customHeight="1">
       <c r="A329" s="9" t="n">
@@ -15449,6 +15794,7 @@
       <c r="N329" s="9" t="n"/>
       <c r="O329" s="9" t="n"/>
       <c r="P329" s="9" t="n"/>
+      <c r="Q329" s="9" t="n"/>
     </row>
     <row r="330" ht="42" customHeight="1">
       <c r="A330" s="7" t="n">
@@ -15493,6 +15839,7 @@
       <c r="N330" s="9" t="n"/>
       <c r="O330" s="9" t="n"/>
       <c r="P330" s="9" t="n"/>
+      <c r="Q330" s="9" t="n"/>
     </row>
     <row r="331" ht="42" customHeight="1">
       <c r="A331" s="9" t="n">
@@ -15541,6 +15888,7 @@
       <c r="N331" s="9" t="n"/>
       <c r="O331" s="9" t="n"/>
       <c r="P331" s="9" t="n"/>
+      <c r="Q331" s="9" t="n"/>
     </row>
     <row r="332" ht="42" customHeight="1">
       <c r="A332" s="7" t="n">
@@ -15589,6 +15937,7 @@
       <c r="N332" s="9" t="n"/>
       <c r="O332" s="9" t="n"/>
       <c r="P332" s="9" t="n"/>
+      <c r="Q332" s="9" t="n"/>
     </row>
     <row r="333" ht="42" customHeight="1">
       <c r="A333" s="9" t="n">
@@ -15633,6 +15982,7 @@
       <c r="N333" s="9" t="n"/>
       <c r="O333" s="9" t="n"/>
       <c r="P333" s="9" t="n"/>
+      <c r="Q333" s="9" t="n"/>
     </row>
     <row r="334" ht="42" customHeight="1">
       <c r="A334" s="7" t="n">
@@ -15681,6 +16031,7 @@
       <c r="N334" s="9" t="n"/>
       <c r="O334" s="9" t="n"/>
       <c r="P334" s="9" t="n"/>
+      <c r="Q334" s="9" t="n"/>
     </row>
     <row r="335" ht="42" customHeight="1">
       <c r="A335" s="9" t="n">
@@ -15725,6 +16076,7 @@
       <c r="N335" s="9" t="n"/>
       <c r="O335" s="9" t="n"/>
       <c r="P335" s="9" t="n"/>
+      <c r="Q335" s="9" t="n"/>
     </row>
     <row r="336" ht="42" customHeight="1">
       <c r="A336" s="7" t="n">
@@ -15769,6 +16121,7 @@
       <c r="N336" s="9" t="n"/>
       <c r="O336" s="9" t="n"/>
       <c r="P336" s="9" t="n"/>
+      <c r="Q336" s="9" t="n"/>
     </row>
     <row r="337" ht="42" customHeight="1">
       <c r="A337" s="9" t="n">
@@ -15813,6 +16166,7 @@
       <c r="N337" s="9" t="n"/>
       <c r="O337" s="9" t="n"/>
       <c r="P337" s="9" t="n"/>
+      <c r="Q337" s="9" t="n"/>
     </row>
     <row r="338" ht="42" customHeight="1">
       <c r="A338" s="7" t="n">
@@ -15861,6 +16215,7 @@
       <c r="N338" s="9" t="n"/>
       <c r="O338" s="9" t="n"/>
       <c r="P338" s="9" t="n"/>
+      <c r="Q338" s="9" t="n"/>
     </row>
     <row r="339" ht="42" customHeight="1">
       <c r="A339" s="9" t="n">
@@ -15909,6 +16264,7 @@
       <c r="N339" s="9" t="n"/>
       <c r="O339" s="9" t="n"/>
       <c r="P339" s="9" t="n"/>
+      <c r="Q339" s="9" t="n"/>
     </row>
     <row r="340" ht="42" customHeight="1">
       <c r="A340" s="7" t="n">
@@ -15957,6 +16313,7 @@
       <c r="N340" s="9" t="n"/>
       <c r="O340" s="9" t="n"/>
       <c r="P340" s="9" t="n"/>
+      <c r="Q340" s="9" t="n"/>
     </row>
     <row r="341" ht="42" customHeight="1">
       <c r="A341" s="9" t="n">
@@ -16001,6 +16358,7 @@
       <c r="N341" s="9" t="n"/>
       <c r="O341" s="9" t="n"/>
       <c r="P341" s="9" t="n"/>
+      <c r="Q341" s="9" t="n"/>
     </row>
     <row r="342" ht="42" customHeight="1">
       <c r="A342" s="7" t="n">
@@ -16045,6 +16403,7 @@
       <c r="N342" s="9" t="n"/>
       <c r="O342" s="9" t="n"/>
       <c r="P342" s="9" t="n"/>
+      <c r="Q342" s="9" t="n"/>
     </row>
     <row r="343" ht="42" customHeight="1">
       <c r="A343" s="9" t="n">
@@ -16089,6 +16448,7 @@
       <c r="N343" s="9" t="n"/>
       <c r="O343" s="9" t="n"/>
       <c r="P343" s="9" t="n"/>
+      <c r="Q343" s="9" t="n"/>
     </row>
     <row r="344" ht="42" customHeight="1">
       <c r="A344" s="7" t="n">
@@ -16133,6 +16493,7 @@
       <c r="N344" s="9" t="n"/>
       <c r="O344" s="9" t="n"/>
       <c r="P344" s="9" t="n"/>
+      <c r="Q344" s="9" t="n"/>
     </row>
     <row r="345" ht="42" customHeight="1">
       <c r="A345" s="9" t="n">
@@ -16177,6 +16538,7 @@
       <c r="N345" s="9" t="n"/>
       <c r="O345" s="9" t="n"/>
       <c r="P345" s="9" t="n"/>
+      <c r="Q345" s="9" t="n"/>
     </row>
     <row r="346" ht="42" customHeight="1">
       <c r="A346" s="7" t="n">
@@ -16225,6 +16587,7 @@
       <c r="N346" s="9" t="n"/>
       <c r="O346" s="9" t="n"/>
       <c r="P346" s="9" t="n"/>
+      <c r="Q346" s="9" t="n"/>
     </row>
     <row r="347" ht="42" customHeight="1">
       <c r="A347" s="9" t="n">
@@ -16269,6 +16632,7 @@
       <c r="N347" s="9" t="n"/>
       <c r="O347" s="9" t="n"/>
       <c r="P347" s="9" t="n"/>
+      <c r="Q347" s="9" t="n"/>
     </row>
     <row r="348" ht="42" customHeight="1">
       <c r="A348" s="7" t="n">
@@ -16313,6 +16677,7 @@
       <c r="N348" s="9" t="n"/>
       <c r="O348" s="9" t="n"/>
       <c r="P348" s="9" t="n"/>
+      <c r="Q348" s="9" t="n"/>
     </row>
     <row r="349" ht="42" customHeight="1">
       <c r="A349" s="9" t="n">
@@ -16357,6 +16722,7 @@
       <c r="N349" s="9" t="n"/>
       <c r="O349" s="9" t="n"/>
       <c r="P349" s="9" t="n"/>
+      <c r="Q349" s="9" t="n"/>
     </row>
     <row r="350" ht="42" customHeight="1">
       <c r="A350" s="7" t="n">
@@ -16405,6 +16771,7 @@
       <c r="N350" s="9" t="n"/>
       <c r="O350" s="9" t="n"/>
       <c r="P350" s="9" t="n"/>
+      <c r="Q350" s="9" t="n"/>
     </row>
     <row r="351" ht="42" customHeight="1">
       <c r="A351" s="9" t="n">
@@ -16453,6 +16820,7 @@
       <c r="N351" s="9" t="n"/>
       <c r="O351" s="9" t="n"/>
       <c r="P351" s="9" t="n"/>
+      <c r="Q351" s="9" t="n"/>
     </row>
     <row r="352" ht="42" customHeight="1">
       <c r="A352" s="7" t="n">
@@ -16497,6 +16865,7 @@
       <c r="N352" s="9" t="n"/>
       <c r="O352" s="9" t="n"/>
       <c r="P352" s="9" t="n"/>
+      <c r="Q352" s="9" t="n"/>
     </row>
     <row r="353" ht="42" customHeight="1">
       <c r="A353" s="9" t="n">
@@ -16541,6 +16910,7 @@
       <c r="N353" s="9" t="n"/>
       <c r="O353" s="9" t="n"/>
       <c r="P353" s="9" t="n"/>
+      <c r="Q353" s="9" t="n"/>
     </row>
     <row r="354" ht="42" customHeight="1">
       <c r="A354" s="7" t="n">
@@ -16589,6 +16959,7 @@
       <c r="N354" s="9" t="n"/>
       <c r="O354" s="9" t="n"/>
       <c r="P354" s="9" t="n"/>
+      <c r="Q354" s="9" t="n"/>
     </row>
     <row r="355" ht="42" customHeight="1">
       <c r="A355" s="9" t="n">
@@ -16633,6 +17004,7 @@
       <c r="N355" s="9" t="n"/>
       <c r="O355" s="9" t="n"/>
       <c r="P355" s="9" t="n"/>
+      <c r="Q355" s="9" t="n"/>
     </row>
     <row r="356" ht="42" customHeight="1">
       <c r="A356" s="7" t="n">
@@ -16677,6 +17049,7 @@
       <c r="N356" s="9" t="n"/>
       <c r="O356" s="9" t="n"/>
       <c r="P356" s="9" t="n"/>
+      <c r="Q356" s="9" t="n"/>
     </row>
     <row r="357" ht="42" customHeight="1">
       <c r="A357" s="9" t="n">
@@ -16721,6 +17094,7 @@
       <c r="N357" s="9" t="n"/>
       <c r="O357" s="9" t="n"/>
       <c r="P357" s="9" t="n"/>
+      <c r="Q357" s="9" t="n"/>
     </row>
     <row r="358" ht="42" customHeight="1">
       <c r="A358" s="7" t="n">
@@ -16765,6 +17139,7 @@
       <c r="N358" s="9" t="n"/>
       <c r="O358" s="9" t="n"/>
       <c r="P358" s="9" t="n"/>
+      <c r="Q358" s="9" t="n"/>
     </row>
     <row r="359" ht="42" customHeight="1">
       <c r="A359" s="9" t="n">
@@ -16809,6 +17184,7 @@
       <c r="N359" s="9" t="n"/>
       <c r="O359" s="9" t="n"/>
       <c r="P359" s="9" t="n"/>
+      <c r="Q359" s="9" t="n"/>
     </row>
     <row r="360" ht="42" customHeight="1">
       <c r="A360" s="7" t="n">
@@ -16853,6 +17229,7 @@
       <c r="N360" s="9" t="n"/>
       <c r="O360" s="9" t="n"/>
       <c r="P360" s="9" t="n"/>
+      <c r="Q360" s="9" t="n"/>
     </row>
     <row r="361" ht="42" customHeight="1">
       <c r="A361" s="9" t="n">
@@ -16897,6 +17274,7 @@
       <c r="N361" s="9" t="n"/>
       <c r="O361" s="9" t="n"/>
       <c r="P361" s="9" t="n"/>
+      <c r="Q361" s="9" t="n"/>
     </row>
     <row r="362" ht="42" customHeight="1">
       <c r="A362" s="7" t="n">
@@ -16941,6 +17319,7 @@
       <c r="N362" s="9" t="n"/>
       <c r="O362" s="9" t="n"/>
       <c r="P362" s="9" t="n"/>
+      <c r="Q362" s="9" t="n"/>
     </row>
     <row r="363" ht="42" customHeight="1">
       <c r="A363" s="9" t="n">
@@ -16985,6 +17364,7 @@
       <c r="N363" s="9" t="n"/>
       <c r="O363" s="9" t="n"/>
       <c r="P363" s="9" t="n"/>
+      <c r="Q363" s="9" t="n"/>
     </row>
     <row r="364" ht="42" customHeight="1">
       <c r="A364" s="7" t="n">
@@ -17029,6 +17409,7 @@
       <c r="N364" s="9" t="n"/>
       <c r="O364" s="9" t="n"/>
       <c r="P364" s="9" t="n"/>
+      <c r="Q364" s="9" t="n"/>
     </row>
     <row r="365" ht="42" customHeight="1">
       <c r="A365" s="9" t="n">
@@ -17073,6 +17454,7 @@
       <c r="N365" s="9" t="n"/>
       <c r="O365" s="9" t="n"/>
       <c r="P365" s="9" t="n"/>
+      <c r="Q365" s="9" t="n"/>
     </row>
     <row r="366" ht="42" customHeight="1">
       <c r="A366" s="7" t="n">
@@ -17117,6 +17499,7 @@
       <c r="N366" s="9" t="n"/>
       <c r="O366" s="9" t="n"/>
       <c r="P366" s="9" t="n"/>
+      <c r="Q366" s="9" t="n"/>
     </row>
     <row r="367" ht="42" customHeight="1">
       <c r="A367" s="9" t="n">
@@ -17165,6 +17548,7 @@
       <c r="N367" s="9" t="n"/>
       <c r="O367" s="9" t="n"/>
       <c r="P367" s="9" t="n"/>
+      <c r="Q367" s="9" t="n"/>
     </row>
     <row r="368" ht="42" customHeight="1">
       <c r="A368" s="7" t="n">
@@ -17213,6 +17597,7 @@
       <c r="N368" s="9" t="n"/>
       <c r="O368" s="9" t="n"/>
       <c r="P368" s="9" t="n"/>
+      <c r="Q368" s="9" t="n"/>
     </row>
     <row r="369" ht="42" customHeight="1">
       <c r="A369" s="9" t="n">
@@ -17261,6 +17646,7 @@
       <c r="N369" s="9" t="n"/>
       <c r="O369" s="9" t="n"/>
       <c r="P369" s="9" t="n"/>
+      <c r="Q369" s="9" t="n"/>
     </row>
     <row r="370" ht="42" customHeight="1">
       <c r="A370" s="7" t="n">
@@ -17309,6 +17695,7 @@
       <c r="N370" s="9" t="n"/>
       <c r="O370" s="9" t="n"/>
       <c r="P370" s="9" t="n"/>
+      <c r="Q370" s="9" t="n"/>
     </row>
     <row r="371" ht="42" customHeight="1">
       <c r="A371" s="9" t="n">
@@ -17353,6 +17740,7 @@
       <c r="N371" s="9" t="n"/>
       <c r="O371" s="9" t="n"/>
       <c r="P371" s="9" t="n"/>
+      <c r="Q371" s="9" t="n"/>
     </row>
     <row r="372" ht="42" customHeight="1">
       <c r="A372" s="7" t="n">
@@ -17397,6 +17785,7 @@
       <c r="N372" s="9" t="n"/>
       <c r="O372" s="9" t="n"/>
       <c r="P372" s="9" t="n"/>
+      <c r="Q372" s="9" t="n"/>
     </row>
     <row r="373" ht="42" customHeight="1">
       <c r="A373" s="9" t="n">
@@ -17441,6 +17830,7 @@
       <c r="N373" s="9" t="n"/>
       <c r="O373" s="9" t="n"/>
       <c r="P373" s="9" t="n"/>
+      <c r="Q373" s="9" t="n"/>
     </row>
     <row r="374" ht="42" customHeight="1">
       <c r="A374" s="7" t="n">
@@ -17485,6 +17875,7 @@
       <c r="N374" s="9" t="n"/>
       <c r="O374" s="9" t="n"/>
       <c r="P374" s="9" t="n"/>
+      <c r="Q374" s="9" t="n"/>
     </row>
     <row r="375" ht="42" customHeight="1">
       <c r="A375" s="9" t="n">
@@ -17529,6 +17920,7 @@
       <c r="N375" s="9" t="n"/>
       <c r="O375" s="9" t="n"/>
       <c r="P375" s="9" t="n"/>
+      <c r="Q375" s="9" t="n"/>
     </row>
     <row r="376" ht="42" customHeight="1">
       <c r="A376" s="7" t="n">
@@ -17573,6 +17965,7 @@
       <c r="N376" s="9" t="n"/>
       <c r="O376" s="9" t="n"/>
       <c r="P376" s="9" t="n"/>
+      <c r="Q376" s="9" t="n"/>
     </row>
     <row r="377" ht="42" customHeight="1">
       <c r="A377" s="9" t="n">
@@ -17617,6 +18010,7 @@
       <c r="N377" s="9" t="n"/>
       <c r="O377" s="9" t="n"/>
       <c r="P377" s="9" t="n"/>
+      <c r="Q377" s="9" t="n"/>
     </row>
     <row r="378" ht="42" customHeight="1">
       <c r="A378" s="7" t="n">
@@ -17661,6 +18055,7 @@
       <c r="N378" s="9" t="n"/>
       <c r="O378" s="9" t="n"/>
       <c r="P378" s="9" t="n"/>
+      <c r="Q378" s="9" t="n"/>
     </row>
     <row r="379" ht="42" customHeight="1">
       <c r="A379" s="9" t="n">
@@ -17709,6 +18104,7 @@
       <c r="N379" s="9" t="n"/>
       <c r="O379" s="9" t="n"/>
       <c r="P379" s="9" t="n"/>
+      <c r="Q379" s="9" t="n"/>
     </row>
     <row r="380" ht="42" customHeight="1">
       <c r="A380" s="7" t="n">
@@ -17753,6 +18149,7 @@
       <c r="N380" s="9" t="n"/>
       <c r="O380" s="9" t="n"/>
       <c r="P380" s="9" t="n"/>
+      <c r="Q380" s="9" t="n"/>
     </row>
     <row r="381" ht="42" customHeight="1">
       <c r="A381" s="9" t="n">
@@ -17797,6 +18194,7 @@
       <c r="N381" s="9" t="n"/>
       <c r="O381" s="9" t="n"/>
       <c r="P381" s="9" t="n"/>
+      <c r="Q381" s="9" t="n"/>
     </row>
     <row r="382" ht="42" customHeight="1">
       <c r="A382" s="7" t="n">
@@ -17845,6 +18243,7 @@
       <c r="N382" s="9" t="n"/>
       <c r="O382" s="9" t="n"/>
       <c r="P382" s="9" t="n"/>
+      <c r="Q382" s="9" t="n"/>
     </row>
     <row r="383" ht="42" customHeight="1">
       <c r="A383" s="9" t="n">
@@ -17889,6 +18288,7 @@
       <c r="N383" s="9" t="n"/>
       <c r="O383" s="9" t="n"/>
       <c r="P383" s="9" t="n"/>
+      <c r="Q383" s="9" t="n"/>
     </row>
     <row r="384" ht="42" customHeight="1">
       <c r="A384" s="7" t="n">
@@ -17933,6 +18333,7 @@
       <c r="N384" s="9" t="n"/>
       <c r="O384" s="9" t="n"/>
       <c r="P384" s="9" t="n"/>
+      <c r="Q384" s="9" t="n"/>
     </row>
     <row r="385" ht="42" customHeight="1">
       <c r="A385" s="9" t="n">
@@ -17977,6 +18378,7 @@
       <c r="N385" s="9" t="n"/>
       <c r="O385" s="9" t="n"/>
       <c r="P385" s="9" t="n"/>
+      <c r="Q385" s="9" t="n"/>
     </row>
     <row r="386" ht="42" customHeight="1">
       <c r="A386" s="7" t="n">
@@ -18021,6 +18423,7 @@
       <c r="N386" s="9" t="n"/>
       <c r="O386" s="9" t="n"/>
       <c r="P386" s="9" t="n"/>
+      <c r="Q386" s="9" t="n"/>
     </row>
     <row r="387" ht="42" customHeight="1">
       <c r="A387" s="9" t="n">
@@ -18069,6 +18472,7 @@
       <c r="N387" s="9" t="n"/>
       <c r="O387" s="9" t="n"/>
       <c r="P387" s="9" t="n"/>
+      <c r="Q387" s="9" t="n"/>
     </row>
     <row r="388" ht="42" customHeight="1">
       <c r="A388" s="7" t="n">
@@ -18113,6 +18517,7 @@
       <c r="N388" s="9" t="n"/>
       <c r="O388" s="9" t="n"/>
       <c r="P388" s="9" t="n"/>
+      <c r="Q388" s="9" t="n"/>
     </row>
     <row r="389" ht="42" customHeight="1">
       <c r="A389" s="9" t="n">
@@ -18157,6 +18562,7 @@
       <c r="N389" s="9" t="n"/>
       <c r="O389" s="9" t="n"/>
       <c r="P389" s="9" t="n"/>
+      <c r="Q389" s="9" t="n"/>
     </row>
     <row r="390" ht="42" customHeight="1">
       <c r="A390" s="7" t="n">
@@ -18201,6 +18607,7 @@
       <c r="N390" s="9" t="n"/>
       <c r="O390" s="9" t="n"/>
       <c r="P390" s="9" t="n"/>
+      <c r="Q390" s="9" t="n"/>
     </row>
     <row r="391" ht="42" customHeight="1">
       <c r="A391" s="9" t="n">
@@ -18249,6 +18656,7 @@
       <c r="N391" s="9" t="n"/>
       <c r="O391" s="9" t="n"/>
       <c r="P391" s="9" t="n"/>
+      <c r="Q391" s="9" t="n"/>
     </row>
     <row r="392" ht="42" customHeight="1">
       <c r="A392" s="7" t="n">
@@ -18297,6 +18705,7 @@
       <c r="N392" s="9" t="n"/>
       <c r="O392" s="9" t="n"/>
       <c r="P392" s="9" t="n"/>
+      <c r="Q392" s="9" t="n"/>
     </row>
     <row r="393" ht="42" customHeight="1">
       <c r="A393" s="9" t="n">
@@ -18341,6 +18750,7 @@
       <c r="N393" s="9" t="n"/>
       <c r="O393" s="9" t="n"/>
       <c r="P393" s="9" t="n"/>
+      <c r="Q393" s="9" t="n"/>
     </row>
     <row r="394" ht="42" customHeight="1">
       <c r="A394" s="7" t="n">
@@ -18385,6 +18795,7 @@
       <c r="N394" s="9" t="n"/>
       <c r="O394" s="9" t="n"/>
       <c r="P394" s="9" t="n"/>
+      <c r="Q394" s="9" t="n"/>
     </row>
     <row r="395" ht="42" customHeight="1">
       <c r="A395" s="9" t="n">
@@ -18429,6 +18840,7 @@
       <c r="N395" s="9" t="n"/>
       <c r="O395" s="9" t="n"/>
       <c r="P395" s="9" t="n"/>
+      <c r="Q395" s="9" t="n"/>
     </row>
     <row r="396" ht="42" customHeight="1">
       <c r="A396" s="7" t="n">
@@ -18473,6 +18885,7 @@
       <c r="N396" s="9" t="n"/>
       <c r="O396" s="9" t="n"/>
       <c r="P396" s="9" t="n"/>
+      <c r="Q396" s="9" t="n"/>
     </row>
     <row r="397" ht="42" customHeight="1">
       <c r="A397" s="9" t="n">
@@ -18517,6 +18930,7 @@
       <c r="N397" s="9" t="n"/>
       <c r="O397" s="9" t="n"/>
       <c r="P397" s="9" t="n"/>
+      <c r="Q397" s="9" t="n"/>
     </row>
     <row r="398" ht="42" customHeight="1">
       <c r="A398" s="7" t="n">
@@ -18565,6 +18979,7 @@
       <c r="N398" s="9" t="n"/>
       <c r="O398" s="9" t="n"/>
       <c r="P398" s="9" t="n"/>
+      <c r="Q398" s="9" t="n"/>
     </row>
     <row r="399" ht="42" customHeight="1">
       <c r="A399" s="9" t="n">
@@ -18613,6 +19028,7 @@
       <c r="N399" s="9" t="n"/>
       <c r="O399" s="9" t="n"/>
       <c r="P399" s="9" t="n"/>
+      <c r="Q399" s="9" t="n"/>
     </row>
     <row r="400" ht="42" customHeight="1">
       <c r="A400" s="7" t="n">
@@ -18657,6 +19073,7 @@
       <c r="N400" s="9" t="n"/>
       <c r="O400" s="9" t="n"/>
       <c r="P400" s="9" t="n"/>
+      <c r="Q400" s="9" t="n"/>
     </row>
     <row r="401" ht="42" customHeight="1">
       <c r="A401" s="9" t="n">
@@ -18701,6 +19118,7 @@
       <c r="N401" s="9" t="n"/>
       <c r="O401" s="9" t="n"/>
       <c r="P401" s="9" t="n"/>
+      <c r="Q401" s="9" t="n"/>
     </row>
     <row r="402" ht="42" customHeight="1">
       <c r="A402" s="7" t="n">
@@ -18745,6 +19163,7 @@
       <c r="N402" s="9" t="n"/>
       <c r="O402" s="9" t="n"/>
       <c r="P402" s="9" t="n"/>
+      <c r="Q402" s="9" t="n"/>
     </row>
     <row r="403" ht="42" customHeight="1">
       <c r="A403" s="9" t="n">
@@ -18793,6 +19212,7 @@
       <c r="N403" s="9" t="n"/>
       <c r="O403" s="9" t="n"/>
       <c r="P403" s="9" t="n"/>
+      <c r="Q403" s="9" t="n"/>
     </row>
     <row r="404" ht="42" customHeight="1">
       <c r="A404" s="7" t="n">
@@ -18837,6 +19257,7 @@
       <c r="N404" s="9" t="n"/>
       <c r="O404" s="9" t="n"/>
       <c r="P404" s="9" t="n"/>
+      <c r="Q404" s="9" t="n"/>
     </row>
     <row r="405" ht="42" customHeight="1">
       <c r="A405" s="9" t="n">
@@ -18881,6 +19302,7 @@
       <c r="N405" s="9" t="n"/>
       <c r="O405" s="9" t="n"/>
       <c r="P405" s="9" t="n"/>
+      <c r="Q405" s="9" t="n"/>
     </row>
     <row r="406" ht="42" customHeight="1">
       <c r="A406" s="7" t="n">
@@ -18929,6 +19351,7 @@
       <c r="N406" s="9" t="n"/>
       <c r="O406" s="9" t="n"/>
       <c r="P406" s="9" t="n"/>
+      <c r="Q406" s="9" t="n"/>
     </row>
     <row r="407" ht="42" customHeight="1">
       <c r="A407" s="9" t="n">
@@ -18973,6 +19396,7 @@
       <c r="N407" s="9" t="n"/>
       <c r="O407" s="9" t="n"/>
       <c r="P407" s="9" t="n"/>
+      <c r="Q407" s="9" t="n"/>
     </row>
     <row r="408" ht="42" customHeight="1">
       <c r="A408" s="7" t="n">
@@ -19021,6 +19445,7 @@
       <c r="N408" s="9" t="n"/>
       <c r="O408" s="9" t="n"/>
       <c r="P408" s="9" t="n"/>
+      <c r="Q408" s="9" t="n"/>
     </row>
     <row r="409" ht="42" customHeight="1">
       <c r="A409" s="9" t="n">
@@ -19065,6 +19490,7 @@
       <c r="N409" s="9" t="n"/>
       <c r="O409" s="9" t="n"/>
       <c r="P409" s="9" t="n"/>
+      <c r="Q409" s="9" t="n"/>
     </row>
     <row r="410" ht="42" customHeight="1">
       <c r="A410" s="7" t="n">
@@ -19109,6 +19535,7 @@
       <c r="N410" s="9" t="n"/>
       <c r="O410" s="9" t="n"/>
       <c r="P410" s="9" t="n"/>
+      <c r="Q410" s="9" t="n"/>
     </row>
     <row r="411" ht="42" customHeight="1">
       <c r="A411" s="9" t="n">
@@ -19153,6 +19580,7 @@
       <c r="N411" s="9" t="n"/>
       <c r="O411" s="9" t="n"/>
       <c r="P411" s="9" t="n"/>
+      <c r="Q411" s="9" t="n"/>
     </row>
     <row r="412" ht="42" customHeight="1">
       <c r="A412" s="7" t="n">
@@ -19201,9 +19629,10 @@
       <c r="N412" s="9" t="n"/>
       <c r="O412" s="9" t="n"/>
       <c r="P412" s="9" t="n"/>
+      <c r="Q412" s="9" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P412"/>
+  <autoFilter ref="A1:Q412"/>
   <dataValidations count="3">
     <dataValidation sqref="L2:L412" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="取值不在允许范围" error="请从下拉列表中选择。" type="list">
       <formula1>"纽扣电池,磁性异物,尖锐异物,硬币或金属钝物,圆球状钝物,果核,长条状异物,塑料或玩具,水银或体温计,食物团块,其他,原文未说明,非异物病例"</formula1>
